--- a/t.xlsx
+++ b/t.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Astra\Documents\projects\1644.icu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB4B490-22B1-4686-95E9-AFF013B8E084}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD0B3BA-8B46-4071-98CD-42734798CC55}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="29400" windowHeight="12640" tabRatio="351" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="29400" windowHeight="12640" tabRatio="351" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="年表" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="429">
   <si>
     <t>朝代</t>
   </si>
@@ -610,10 +610,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>法国铁面人为明太子朱慈烺</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>满清篡改宋史，将开头 中间 结尾的几个年号保留，其他删除。导致宋每个年号特别短，日食特别多</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -622,14 +618,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>土木堡可能在德国</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>满清八旗对应着北欧8国，颜色高度相似</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>楼兰在古诗里有万里之遥，可能在欧洲</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -647,10 +635,6 @@
   </si>
   <si>
     <t>提倡汉族火葬，计划生育的官员专家是满族</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>华伦天奴创始人家里放很多满清画，估计是满清后裔</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -1503,6 +1487,246 @@
   <si>
     <t>（西汉建立：刘邦称帝（前202）→文景之治；七国之乱（前154）→汉武帝：推恩令/盐铁专卖/独尊儒术/击匈奴/丝绸之路凿空（张骞）；王莽篡汉（AD 9）→光武中兴）</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>曾仕强也不敢明着跟满清势力作对，他是销售额最高的华人讲师。他曾经提到，很多神仙和历代皇帝都转世了，包括崇祯皇帝。因为这个时代不搏一搏将是万劫不复。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>曾仕强说老人不会老，小孩长不大，暗指人口贩卖产业提取干细胞</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>满系艺人给东南亚犯罪集团祝寿和贺新年，后来很多声音洗地。那里简直就是托克所的延续</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>西方人喜欢讲屠龙，屠龙以后会爆金币，指的可能就是消灭中国</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>万里长城在欧洲也有，它不是防御工事而是军用高速公路，古代中国可能占领着整个亚欧大陆</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>瑞士，意大利都有很多榫卯老房子，永济桥那样的桥，很可能是华人聚集地</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>英文发音很多跟客家话粤语相似，很可能来源于汉语</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>很多人鼓吹佳绒语是古汉语</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>实际客家话和粤语才是古汉语，没那么难懂</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>土木堡可能在德国，很多当前的地名可能在欧洲，被人故意篡改到东亚</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>《路史》里的东西被刻意淡化了，信史不信，而去信西方伪史。上古就有很灿烂的文明</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>周礼记载的国家机关复杂度不亚于今日，也许版图远超认知</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>潮汕信仰太阳公是崇祯，他可能并不是上吊而是战死</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>永久残疾性质的裹脚是清朝产物，满清牵强附会地伪造魏晋时期就有裹脚</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>猎巫行动专门谋害懂草药，给人治病的所谓女巫可能是残留华夏子民</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>耶稣可能是崇祯，他们的年龄，遇害时间都很相似，生日甚至同一天</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>西方强调古埃及文明的灿烂，摩亨佐这种都拉出来</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>为了掩盖中华文明的灿烂</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>满清托克所，柳叶边城墙，人口贩卖，系统性地消灭各族人口（航海日志）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>解手可能来自于托克所里的华人奴隶要绑手，上厕所才解开</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>汗衫实际是汉衫。穿在里面，汉人在满清只有婴儿襁褓和寿衣允许使用汉服</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿汉服的干尸“黄拙吾”意为皇出吾。此人六根脚趾，是洪承畴，海宁洪氏取代了满清皇族</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>真康熙病死，归来太高，是假冒的，换了种，满语不会讲</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>满清有多次换种，奴儿哈只血统早已失传</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>从雕塑艺术来看，满清憎恨烈士，汉人，明臣，美化洪承畴，说明甩不掉他</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>皇台吉承认用心理战让崇祯杀袁崇焕，实则可能反过来，袁确实反叛。是为了丑化明廷</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>满清修明史写崇祯凌迟处死袁，实则满清十大酷刑是清朝才有</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>EXO首期四个华人，分别代表着官-鹿晗，富-黄子韬，芒果系-张艺兴，满系-吴亦凡（高奢）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>清华大学就是清+华，是美国用满清赔款捐赠。清华美院屁股尤其歪</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>法国铁面人为明太子朱慈烺，在他之后西方迅速崛起</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>满清八旗对应着北欧8国，颜色高度相似。北欧是反华大本营</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛的作品可能被篡改，例如批判大汉族主义等言论，没有交叉证明记录，仅有文章</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛，周可能被毒害，身体本来硬朗，差不多同一时间急转直下，而且都是癌症</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>孙文说革命尚未成功，毛主席也称辛亥革命没有完成，只能用人民英雄纪念碑表达立场</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>建国后需要钱，可能满遗打钱了，溥仪不处死可以理解，后来还当政协委员有点过头</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>多个叛党叛国的满族人，百度百科被改成汉族</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>创办皇汉网，宣传极端言论的是满族人</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>满遗曾经搞复辟运动，遭到打击但可能不够彻底</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>华伦天奴创始人家里放很多满清画，估计是满清后裔。高奢品牌都搞丑化华人那一套</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>满遗热衷于满语复兴，颁金节等，高奢广告多推行以满代华，让汉服变和服。实则旗袍马褂瓜皮帽并非汉服而是满服</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>厂字领蜈蚣扣的满服跟俄罗斯布里亚特族完全一样。这是蒙古的一支，意为“森林的”</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>印尼人和满人有吃人传统，故朊病毒抗体高，白人也偏高。实锤其南下边打边吃的做法，史上最惨烈</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>实录记载满清部队据守城市被明军围困，最终吃光城中人而全灭。明军找出堆积如山的切了不要的女性阴部数吨</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>布里亚特篡夺女真族，改名满洲，改名满族。改金国为清国。之前，女真族已经基本汉化（完颜系）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>国内有巨大成吉思汗雕像，还有许多美化努尔哈只，施琅等汉奸的雕像，一定程度上说明他们的自身认知</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>满遗似乎认古中山国（白狄）为远祖，以蒙古为先祖，以奴儿哈只为先祖，并有三叉戟作为他们的标识</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>新华字典旧版“旗”的组词为五星红旗。新版为 八旗，并有相关注释</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>改开前教科书为丰子恺定版，插画漂亮。后面越改越歪，直至“毒教材”。领导留言板直接下架教育部投诉入口</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>宣扬黑人入华，难民入华的活动家与犹太人关系深，意图破坏所有纯净血统的凝聚力，因为犹太吃过这个亏（德三）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>日本有爱新觉罗社，满系与“瑞穗”家族关系大，满洲国为日本扶持，溥仪曾投靠日本</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>溥仪的哥哥爱新觉罗宪军主导参与731事件，日，满，犹太可能深度合作</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>非典，新冠可能均为投毒，明末鼠疫可能是投毒，因为疫情发展与战事完全吻合</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>有网友录视频说日本人满人在国内非常多通婚和聚居，可能与日本人学校有关</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>其实真正的满族只有爱新觉罗，其他都是女真族，例如钮钴禄氏，叶赫那拉</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>改开后出现一批满系艺人，如那英，新生代娱乐圈基本不再有满系</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹿晗关晓彤分手，很可能因为鹿晗属于官二代，而关晓彤属于满系艺人</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>达芬奇等许多西方科学家艺术家，都说是做梦的时候找到灵感，发明了xx。而且他们都没有后代，可能是翻译永乐大典的知识</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>文化战强度很高，你说永乐大典里有科技，水军就说里面有光刻机，纯串</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据中药材考证，某些药材像欧洲植物，佐证我们曾经有更大领土</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>今玉门关 铁门关 周围一马平川的戈壁，压根没鸟用。实际玉门关在匈牙利，铁门关在欧洲的铁门国家公园。隋朝挖的运河在欧洲</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2195,7 +2419,7 @@
       <c r="P1" s="10"/>
       <c r="Q1" s="10"/>
       <c r="R1" s="10" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="S1" s="10"/>
       <c r="T1" s="10"/>
@@ -2248,19 +2472,19 @@
         <v>64</v>
       </c>
       <c r="R2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -2309,19 +2533,19 @@
         <v>61</v>
       </c>
       <c r="R3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="V3" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -2370,19 +2594,19 @@
         <v>62</v>
       </c>
       <c r="R4" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="V4" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2431,19 +2655,19 @@
         <v>80</v>
       </c>
       <c r="R5" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="V5" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2492,19 +2716,19 @@
         <v>69</v>
       </c>
       <c r="R6" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="V6" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2553,19 +2777,19 @@
         <v>68</v>
       </c>
       <c r="R7" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="V7" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2614,19 +2838,19 @@
         <v>77</v>
       </c>
       <c r="R8" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="V8" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2675,19 +2899,19 @@
         <v>78</v>
       </c>
       <c r="R9" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="V9" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2736,19 +2960,19 @@
         <v>79</v>
       </c>
       <c r="R10" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="V10" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="V10" s="1" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2797,19 +3021,19 @@
         <v>82</v>
       </c>
       <c r="R11" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="V11" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2858,19 +3082,19 @@
         <v>76</v>
       </c>
       <c r="R12" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="V12" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="V12" s="1" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2919,19 +3143,19 @@
         <v>75</v>
       </c>
       <c r="R13" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="V13" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="V13" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -2980,19 +3204,19 @@
         <v>63</v>
       </c>
       <c r="R14" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="V14" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="V14" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3041,19 +3265,19 @@
         <v>83</v>
       </c>
       <c r="R15" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="V15" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3102,19 +3326,19 @@
         <v>53</v>
       </c>
       <c r="R16" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="V16" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="V16" s="1" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3162,19 +3386,19 @@
         <v>65</v>
       </c>
       <c r="R17" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="V17" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="V17" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3222,19 +3446,19 @@
         <v>13</v>
       </c>
       <c r="R18" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="V18" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="U18" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="V18" s="1" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3282,19 +3506,19 @@
         <v>84</v>
       </c>
       <c r="R19" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="V19" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="V19" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3339,19 +3563,19 @@
         <v>262</v>
       </c>
       <c r="R20" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="V20" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="V20" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3396,19 +3620,19 @@
         <v>332</v>
       </c>
       <c r="R21" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="V21" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="V21" s="1" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3456,19 +3680,19 @@
         <v>18</v>
       </c>
       <c r="R22" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="V22" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="V22" s="1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3513,19 +3737,19 @@
         <v>439</v>
       </c>
       <c r="R23" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="V23" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="V23" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3570,19 +3794,19 @@
         <v>489</v>
       </c>
       <c r="R24" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="V24" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="V24" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3627,19 +3851,19 @@
         <v>959</v>
       </c>
       <c r="R25" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="V25" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3684,19 +3908,19 @@
         <v>1513</v>
       </c>
       <c r="R26" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="V26" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="U26" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="V26" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3741,19 +3965,19 @@
         <v>1788</v>
       </c>
       <c r="R27" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="V27" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="V27" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3798,19 +4022,19 @@
         <v>2337</v>
       </c>
       <c r="R28" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="V28" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="S28" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="T28" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="U28" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="V28" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3858,19 +4082,19 @@
         <v>50</v>
       </c>
       <c r="R29" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="V29" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="U29" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="V29" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3918,19 +4142,19 @@
         <v>27</v>
       </c>
       <c r="R30" s="7" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -3978,19 +4202,19 @@
         <v>29</v>
       </c>
       <c r="R31" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="V31" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="U31" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="V31" s="1" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4038,19 +4262,19 @@
         <v>31</v>
       </c>
       <c r="R32" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="V32" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="V32" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4095,19 +4319,19 @@
         <v>4206</v>
       </c>
       <c r="R33" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="V33" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="V33" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4152,19 +4376,19 @@
         <v>4257</v>
       </c>
       <c r="R34" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="V34" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="V34" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4209,19 +4433,19 @@
         <v>4360</v>
       </c>
       <c r="R35" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="V35" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="S35" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="T35" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="U35" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="V35" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4266,19 +4490,19 @@
         <v>4529</v>
       </c>
       <c r="R36" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="V36" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="S36" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="T36" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="U36" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="V36" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="37" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4326,13 +4550,13 @@
         <v>37</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4380,19 +4604,19 @@
         <v>39</v>
       </c>
       <c r="R38" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="S38" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="U38" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="V38" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="S38" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="V38" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4437,19 +4661,19 @@
         <v>4582</v>
       </c>
       <c r="R39" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="S39" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="U39" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="V39" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="S39" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="U39" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="V39" s="1" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4497,19 +4721,19 @@
         <v>42</v>
       </c>
       <c r="R40" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="S40" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="V40" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="T40" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="U40" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="V40" s="1" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="41" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4554,19 +4778,19 @@
         <v>5682</v>
       </c>
       <c r="R41" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="S41" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="T41" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="V41" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="S41" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="T41" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="U41" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="V41" s="1" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="42" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4614,16 +4838,16 @@
         <v>45</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="43" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4671,19 +4895,19 @@
         <v>47</v>
       </c>
       <c r="R43" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="S43" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="V43" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="S43" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="T43" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="V43" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="44" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -4743,7 +4967,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7293523-8A88-4FA8-8AD8-9CEC8BA3DC9C}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.26953125" customWidth="1"/>
@@ -4784,7 +5008,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>97</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4792,7 +5016,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4800,7 +5024,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4808,7 +5032,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>100</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4816,7 +5040,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>101</v>
+        <v>399</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -4824,7 +5048,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -4832,7 +5056,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4840,7 +5064,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -4848,7 +5072,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -4856,7 +5080,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -4864,7 +5088,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>107</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -4872,7 +5096,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -4880,7 +5104,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -4888,7 +5112,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -4896,7 +5120,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -4904,7 +5128,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -4912,7 +5136,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -4920,18 +5144,435 @@
         <v>20</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>116</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>428</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA240CE6-07FC-4E34-B886-D2C08CA4BB15}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7265625" customWidth="1"/>
@@ -4982,10 +5623,37 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5004,853 +5672,853 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" t="s">
         <v>117</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>118</v>
-      </c>
-      <c r="C1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2" t="s">
         <v>123</v>
       </c>
-      <c r="B2" t="s">
+      <c r="F2" t="s">
         <v>124</v>
-      </c>
-      <c r="C2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" t="s">
         <v>129</v>
       </c>
-      <c r="B3" t="s">
+      <c r="F3" t="s">
         <v>130</v>
-      </c>
-      <c r="C3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" t="s">
         <v>135</v>
       </c>
-      <c r="B4" t="s">
+      <c r="F4" t="s">
         <v>136</v>
-      </c>
-      <c r="C4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F4" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" t="s">
         <v>141</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5" t="s">
         <v>142</v>
-      </c>
-      <c r="C5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D5" t="s">
-        <v>144</v>
-      </c>
-      <c r="E5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F5" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E6" t="s">
         <v>147</v>
       </c>
-      <c r="B6" t="s">
+      <c r="F6" t="s">
         <v>148</v>
-      </c>
-      <c r="C6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E6" t="s">
-        <v>151</v>
-      </c>
-      <c r="F6" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" t="s">
         <v>153</v>
       </c>
-      <c r="B7" t="s">
+      <c r="F7" t="s">
         <v>154</v>
-      </c>
-      <c r="C7" t="s">
-        <v>155</v>
-      </c>
-      <c r="D7" t="s">
-        <v>156</v>
-      </c>
-      <c r="E7" t="s">
-        <v>157</v>
-      </c>
-      <c r="F7" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" t="s">
+        <v>158</v>
+      </c>
+      <c r="E8" t="s">
         <v>159</v>
       </c>
-      <c r="B8" t="s">
+      <c r="F8" t="s">
         <v>160</v>
-      </c>
-      <c r="C8" t="s">
-        <v>161</v>
-      </c>
-      <c r="D8" t="s">
-        <v>162</v>
-      </c>
-      <c r="E8" t="s">
-        <v>163</v>
-      </c>
-      <c r="F8" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E9" t="s">
         <v>165</v>
       </c>
-      <c r="B9" t="s">
+      <c r="F9" t="s">
         <v>166</v>
-      </c>
-      <c r="C9" t="s">
-        <v>167</v>
-      </c>
-      <c r="D9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E9" t="s">
-        <v>169</v>
-      </c>
-      <c r="F9" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" t="s">
         <v>171</v>
       </c>
-      <c r="B10" t="s">
+      <c r="F10" t="s">
         <v>172</v>
-      </c>
-      <c r="C10" t="s">
-        <v>173</v>
-      </c>
-      <c r="D10" t="s">
-        <v>174</v>
-      </c>
-      <c r="E10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F10" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B11" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E11" t="s">
         <v>177</v>
       </c>
-      <c r="B11" t="s">
+      <c r="F11" t="s">
         <v>178</v>
-      </c>
-      <c r="C11" t="s">
-        <v>179</v>
-      </c>
-      <c r="D11" t="s">
-        <v>180</v>
-      </c>
-      <c r="E11" t="s">
-        <v>181</v>
-      </c>
-      <c r="F11" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" t="s">
+        <v>182</v>
+      </c>
+      <c r="E12" t="s">
         <v>183</v>
       </c>
-      <c r="B12" t="s">
+      <c r="F12" t="s">
         <v>184</v>
-      </c>
-      <c r="C12" t="s">
-        <v>185</v>
-      </c>
-      <c r="D12" t="s">
-        <v>186</v>
-      </c>
-      <c r="E12" t="s">
-        <v>187</v>
-      </c>
-      <c r="F12" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C13" t="s">
+        <v>187</v>
+      </c>
+      <c r="D13" t="s">
+        <v>188</v>
+      </c>
+      <c r="E13" t="s">
         <v>189</v>
       </c>
-      <c r="B13" t="s">
+      <c r="F13" t="s">
         <v>190</v>
-      </c>
-      <c r="C13" t="s">
-        <v>191</v>
-      </c>
-      <c r="D13" t="s">
-        <v>192</v>
-      </c>
-      <c r="E13" t="s">
-        <v>193</v>
-      </c>
-      <c r="F13" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C14" t="s">
+        <v>193</v>
+      </c>
+      <c r="D14" t="s">
+        <v>194</v>
+      </c>
+      <c r="E14" t="s">
         <v>195</v>
       </c>
-      <c r="B14" t="s">
+      <c r="F14" t="s">
         <v>196</v>
-      </c>
-      <c r="C14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D14" t="s">
-        <v>198</v>
-      </c>
-      <c r="E14" t="s">
-        <v>199</v>
-      </c>
-      <c r="F14" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>197</v>
+      </c>
+      <c r="B15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C15" t="s">
+        <v>199</v>
+      </c>
+      <c r="D15" t="s">
+        <v>200</v>
+      </c>
+      <c r="E15" t="s">
         <v>201</v>
       </c>
-      <c r="B15" t="s">
+      <c r="F15" t="s">
         <v>202</v>
-      </c>
-      <c r="C15" t="s">
-        <v>203</v>
-      </c>
-      <c r="D15" t="s">
-        <v>204</v>
-      </c>
-      <c r="E15" t="s">
-        <v>205</v>
-      </c>
-      <c r="F15" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>203</v>
+      </c>
+      <c r="B16" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D16" t="s">
+        <v>206</v>
+      </c>
+      <c r="E16" t="s">
         <v>207</v>
       </c>
-      <c r="B16" t="s">
+      <c r="F16" t="s">
         <v>208</v>
-      </c>
-      <c r="C16" t="s">
-        <v>209</v>
-      </c>
-      <c r="D16" t="s">
-        <v>210</v>
-      </c>
-      <c r="E16" t="s">
-        <v>211</v>
-      </c>
-      <c r="F16" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" t="s">
+        <v>210</v>
+      </c>
+      <c r="C17" t="s">
+        <v>211</v>
+      </c>
+      <c r="D17" t="s">
+        <v>212</v>
+      </c>
+      <c r="E17" t="s">
         <v>213</v>
       </c>
-      <c r="B17" t="s">
+      <c r="F17" t="s">
         <v>214</v>
-      </c>
-      <c r="C17" t="s">
-        <v>215</v>
-      </c>
-      <c r="D17" t="s">
-        <v>216</v>
-      </c>
-      <c r="E17" t="s">
-        <v>217</v>
-      </c>
-      <c r="F17" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>215</v>
+      </c>
+      <c r="B18" t="s">
+        <v>216</v>
+      </c>
+      <c r="C18" t="s">
+        <v>217</v>
+      </c>
+      <c r="D18" t="s">
+        <v>218</v>
+      </c>
+      <c r="E18" t="s">
         <v>219</v>
       </c>
-      <c r="B18" t="s">
+      <c r="F18" t="s">
         <v>220</v>
-      </c>
-      <c r="C18" t="s">
-        <v>221</v>
-      </c>
-      <c r="D18" t="s">
-        <v>222</v>
-      </c>
-      <c r="E18" t="s">
-        <v>223</v>
-      </c>
-      <c r="F18" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B19" t="s">
+        <v>222</v>
+      </c>
+      <c r="C19" t="s">
+        <v>223</v>
+      </c>
+      <c r="D19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E19" t="s">
         <v>225</v>
       </c>
-      <c r="B19" t="s">
+      <c r="F19" t="s">
         <v>226</v>
-      </c>
-      <c r="C19" t="s">
-        <v>227</v>
-      </c>
-      <c r="D19" t="s">
-        <v>228</v>
-      </c>
-      <c r="E19" t="s">
-        <v>229</v>
-      </c>
-      <c r="F19" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>227</v>
+      </c>
+      <c r="B20" t="s">
+        <v>228</v>
+      </c>
+      <c r="C20" t="s">
+        <v>229</v>
+      </c>
+      <c r="D20" t="s">
+        <v>230</v>
+      </c>
+      <c r="E20" t="s">
         <v>231</v>
       </c>
-      <c r="B20" t="s">
+      <c r="F20" t="s">
         <v>232</v>
-      </c>
-      <c r="C20" t="s">
-        <v>233</v>
-      </c>
-      <c r="D20" t="s">
-        <v>234</v>
-      </c>
-      <c r="E20" t="s">
-        <v>235</v>
-      </c>
-      <c r="F20" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>233</v>
+      </c>
+      <c r="B21" t="s">
+        <v>234</v>
+      </c>
+      <c r="C21" t="s">
+        <v>235</v>
+      </c>
+      <c r="D21" t="s">
+        <v>236</v>
+      </c>
+      <c r="E21" t="s">
         <v>237</v>
       </c>
-      <c r="B21" t="s">
+      <c r="F21" t="s">
         <v>238</v>
-      </c>
-      <c r="C21" t="s">
-        <v>239</v>
-      </c>
-      <c r="D21" t="s">
-        <v>240</v>
-      </c>
-      <c r="E21" t="s">
-        <v>241</v>
-      </c>
-      <c r="F21" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>239</v>
+      </c>
+      <c r="B22" t="s">
+        <v>240</v>
+      </c>
+      <c r="C22" t="s">
+        <v>241</v>
+      </c>
+      <c r="D22" t="s">
+        <v>242</v>
+      </c>
+      <c r="E22" t="s">
         <v>243</v>
       </c>
-      <c r="B22" t="s">
+      <c r="F22" t="s">
         <v>244</v>
-      </c>
-      <c r="C22" t="s">
-        <v>245</v>
-      </c>
-      <c r="D22" t="s">
-        <v>246</v>
-      </c>
-      <c r="E22" t="s">
-        <v>247</v>
-      </c>
-      <c r="F22" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>245</v>
+      </c>
+      <c r="B23" t="s">
+        <v>246</v>
+      </c>
+      <c r="C23" t="s">
+        <v>247</v>
+      </c>
+      <c r="D23" t="s">
+        <v>248</v>
+      </c>
+      <c r="E23" t="s">
         <v>249</v>
       </c>
-      <c r="B23" t="s">
+      <c r="F23" t="s">
         <v>250</v>
-      </c>
-      <c r="C23" t="s">
-        <v>251</v>
-      </c>
-      <c r="D23" t="s">
-        <v>252</v>
-      </c>
-      <c r="E23" t="s">
-        <v>253</v>
-      </c>
-      <c r="F23" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>251</v>
+      </c>
+      <c r="B24" t="s">
+        <v>252</v>
+      </c>
+      <c r="C24" t="s">
+        <v>253</v>
+      </c>
+      <c r="D24" t="s">
+        <v>254</v>
+      </c>
+      <c r="E24" t="s">
         <v>255</v>
       </c>
-      <c r="B24" t="s">
+      <c r="F24" t="s">
         <v>256</v>
-      </c>
-      <c r="C24" t="s">
-        <v>257</v>
-      </c>
-      <c r="D24" t="s">
-        <v>258</v>
-      </c>
-      <c r="E24" t="s">
-        <v>259</v>
-      </c>
-      <c r="F24" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>257</v>
+      </c>
+      <c r="B25" t="s">
+        <v>258</v>
+      </c>
+      <c r="C25" t="s">
+        <v>259</v>
+      </c>
+      <c r="D25" t="s">
+        <v>260</v>
+      </c>
+      <c r="E25" t="s">
         <v>261</v>
       </c>
-      <c r="B25" t="s">
+      <c r="F25" t="s">
         <v>262</v>
-      </c>
-      <c r="C25" t="s">
-        <v>263</v>
-      </c>
-      <c r="D25" t="s">
-        <v>264</v>
-      </c>
-      <c r="E25" t="s">
-        <v>265</v>
-      </c>
-      <c r="F25" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B26" t="s">
+        <v>264</v>
+      </c>
+      <c r="C26" t="s">
+        <v>265</v>
+      </c>
+      <c r="D26" t="s">
+        <v>266</v>
+      </c>
+      <c r="E26" t="s">
         <v>267</v>
       </c>
-      <c r="B26" t="s">
+      <c r="F26" t="s">
         <v>268</v>
-      </c>
-      <c r="C26" t="s">
-        <v>269</v>
-      </c>
-      <c r="D26" t="s">
-        <v>270</v>
-      </c>
-      <c r="E26" t="s">
-        <v>271</v>
-      </c>
-      <c r="F26" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>269</v>
+      </c>
+      <c r="B27" t="s">
+        <v>270</v>
+      </c>
+      <c r="C27" t="s">
+        <v>271</v>
+      </c>
+      <c r="D27" t="s">
+        <v>272</v>
+      </c>
+      <c r="E27" t="s">
         <v>273</v>
       </c>
-      <c r="B27" t="s">
+      <c r="F27" t="s">
         <v>274</v>
-      </c>
-      <c r="C27" t="s">
-        <v>275</v>
-      </c>
-      <c r="D27" t="s">
-        <v>276</v>
-      </c>
-      <c r="E27" t="s">
-        <v>277</v>
-      </c>
-      <c r="F27" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>275</v>
+      </c>
+      <c r="B28" t="s">
+        <v>276</v>
+      </c>
+      <c r="C28" t="s">
+        <v>277</v>
+      </c>
+      <c r="D28" t="s">
+        <v>278</v>
+      </c>
+      <c r="E28" t="s">
         <v>279</v>
       </c>
-      <c r="B28" t="s">
+      <c r="F28" t="s">
         <v>280</v>
-      </c>
-      <c r="C28" t="s">
-        <v>281</v>
-      </c>
-      <c r="D28" t="s">
-        <v>282</v>
-      </c>
-      <c r="E28" t="s">
-        <v>283</v>
-      </c>
-      <c r="F28" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B29" t="s">
+        <v>282</v>
+      </c>
+      <c r="C29" t="s">
+        <v>283</v>
+      </c>
+      <c r="D29" t="s">
+        <v>284</v>
+      </c>
+      <c r="E29" t="s">
         <v>285</v>
       </c>
-      <c r="B29" t="s">
+      <c r="F29" t="s">
         <v>286</v>
-      </c>
-      <c r="C29" t="s">
-        <v>287</v>
-      </c>
-      <c r="D29" t="s">
-        <v>288</v>
-      </c>
-      <c r="E29" t="s">
-        <v>289</v>
-      </c>
-      <c r="F29" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>287</v>
+      </c>
+      <c r="B30" t="s">
+        <v>288</v>
+      </c>
+      <c r="C30" t="s">
+        <v>289</v>
+      </c>
+      <c r="D30" t="s">
+        <v>290</v>
+      </c>
+      <c r="E30" t="s">
         <v>291</v>
       </c>
-      <c r="B30" t="s">
+      <c r="F30" t="s">
         <v>292</v>
-      </c>
-      <c r="C30" t="s">
-        <v>293</v>
-      </c>
-      <c r="D30" t="s">
-        <v>294</v>
-      </c>
-      <c r="E30" t="s">
-        <v>295</v>
-      </c>
-      <c r="F30" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>293</v>
+      </c>
+      <c r="B31" t="s">
+        <v>294</v>
+      </c>
+      <c r="C31" t="s">
+        <v>295</v>
+      </c>
+      <c r="D31" t="s">
+        <v>296</v>
+      </c>
+      <c r="E31" t="s">
         <v>297</v>
       </c>
-      <c r="B31" t="s">
+      <c r="F31" t="s">
         <v>298</v>
-      </c>
-      <c r="C31" t="s">
-        <v>299</v>
-      </c>
-      <c r="D31" t="s">
-        <v>300</v>
-      </c>
-      <c r="E31" t="s">
-        <v>301</v>
-      </c>
-      <c r="F31" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>299</v>
+      </c>
+      <c r="B32" t="s">
+        <v>300</v>
+      </c>
+      <c r="C32" t="s">
+        <v>301</v>
+      </c>
+      <c r="D32" t="s">
+        <v>302</v>
+      </c>
+      <c r="E32" t="s">
         <v>303</v>
       </c>
-      <c r="B32" t="s">
+      <c r="F32" t="s">
         <v>304</v>
-      </c>
-      <c r="C32" t="s">
-        <v>305</v>
-      </c>
-      <c r="D32" t="s">
-        <v>306</v>
-      </c>
-      <c r="E32" t="s">
-        <v>307</v>
-      </c>
-      <c r="F32" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>305</v>
+      </c>
+      <c r="B33" t="s">
+        <v>306</v>
+      </c>
+      <c r="C33" t="s">
+        <v>307</v>
+      </c>
+      <c r="D33" t="s">
+        <v>308</v>
+      </c>
+      <c r="E33" t="s">
         <v>309</v>
       </c>
-      <c r="B33" t="s">
+      <c r="F33" t="s">
         <v>310</v>
-      </c>
-      <c r="C33" t="s">
-        <v>311</v>
-      </c>
-      <c r="D33" t="s">
-        <v>312</v>
-      </c>
-      <c r="E33" t="s">
-        <v>313</v>
-      </c>
-      <c r="F33" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>311</v>
+      </c>
+      <c r="B34" t="s">
+        <v>312</v>
+      </c>
+      <c r="C34" t="s">
+        <v>313</v>
+      </c>
+      <c r="D34" t="s">
+        <v>314</v>
+      </c>
+      <c r="E34" t="s">
         <v>315</v>
       </c>
-      <c r="B34" t="s">
+      <c r="F34" t="s">
         <v>316</v>
-      </c>
-      <c r="C34" t="s">
-        <v>317</v>
-      </c>
-      <c r="D34" t="s">
-        <v>318</v>
-      </c>
-      <c r="E34" t="s">
-        <v>319</v>
-      </c>
-      <c r="F34" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>317</v>
+      </c>
+      <c r="B35" t="s">
+        <v>318</v>
+      </c>
+      <c r="C35" t="s">
+        <v>319</v>
+      </c>
+      <c r="D35" t="s">
+        <v>320</v>
+      </c>
+      <c r="E35" t="s">
         <v>321</v>
       </c>
-      <c r="B35" t="s">
+      <c r="F35" t="s">
         <v>322</v>
-      </c>
-      <c r="C35" t="s">
-        <v>323</v>
-      </c>
-      <c r="D35" t="s">
-        <v>324</v>
-      </c>
-      <c r="E35" t="s">
-        <v>325</v>
-      </c>
-      <c r="F35" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>323</v>
+      </c>
+      <c r="B36" t="s">
+        <v>324</v>
+      </c>
+      <c r="C36" t="s">
+        <v>325</v>
+      </c>
+      <c r="D36" t="s">
+        <v>326</v>
+      </c>
+      <c r="E36" t="s">
         <v>327</v>
       </c>
-      <c r="B36" t="s">
+      <c r="F36" t="s">
         <v>328</v>
-      </c>
-      <c r="C36" t="s">
-        <v>329</v>
-      </c>
-      <c r="D36" t="s">
-        <v>330</v>
-      </c>
-      <c r="E36" t="s">
-        <v>331</v>
-      </c>
-      <c r="F36" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B37" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C37" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D37" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>333</v>
+      </c>
+      <c r="B38" t="s">
+        <v>334</v>
+      </c>
+      <c r="C38" t="s">
+        <v>335</v>
+      </c>
+      <c r="D38" t="s">
+        <v>336</v>
+      </c>
+      <c r="E38" t="s">
         <v>337</v>
       </c>
-      <c r="B38" t="s">
+      <c r="F38" t="s">
         <v>338</v>
-      </c>
-      <c r="C38" t="s">
-        <v>339</v>
-      </c>
-      <c r="D38" t="s">
-        <v>340</v>
-      </c>
-      <c r="E38" t="s">
-        <v>341</v>
-      </c>
-      <c r="F38" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>339</v>
+      </c>
+      <c r="B39" t="s">
+        <v>340</v>
+      </c>
+      <c r="C39" t="s">
+        <v>341</v>
+      </c>
+      <c r="D39" t="s">
+        <v>342</v>
+      </c>
+      <c r="E39" t="s">
         <v>343</v>
       </c>
-      <c r="B39" t="s">
+      <c r="F39" t="s">
         <v>344</v>
-      </c>
-      <c r="C39" t="s">
-        <v>345</v>
-      </c>
-      <c r="D39" t="s">
-        <v>346</v>
-      </c>
-      <c r="E39" t="s">
-        <v>347</v>
-      </c>
-      <c r="F39" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>345</v>
+      </c>
+      <c r="B40" t="s">
+        <v>346</v>
+      </c>
+      <c r="C40" t="s">
+        <v>347</v>
+      </c>
+      <c r="D40" t="s">
+        <v>348</v>
+      </c>
+      <c r="E40" t="s">
         <v>349</v>
       </c>
-      <c r="B40" t="s">
+      <c r="F40" t="s">
         <v>350</v>
-      </c>
-      <c r="C40" t="s">
-        <v>351</v>
-      </c>
-      <c r="D40" t="s">
-        <v>352</v>
-      </c>
-      <c r="E40" t="s">
-        <v>353</v>
-      </c>
-      <c r="F40" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B41" t="s">
+        <v>351</v>
+      </c>
+      <c r="C41" t="s">
+        <v>352</v>
+      </c>
+      <c r="D41" t="s">
+        <v>353</v>
+      </c>
+      <c r="E41" t="s">
+        <v>354</v>
+      </c>
+      <c r="F41" t="s">
         <v>355</v>
-      </c>
-      <c r="C41" t="s">
-        <v>356</v>
-      </c>
-      <c r="D41" t="s">
-        <v>357</v>
-      </c>
-      <c r="E41" t="s">
-        <v>358</v>
-      </c>
-      <c r="F41" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>356</v>
+      </c>
+      <c r="B42" t="s">
+        <v>357</v>
+      </c>
+      <c r="C42" t="s">
+        <v>358</v>
+      </c>
+      <c r="D42" t="s">
+        <v>359</v>
+      </c>
+      <c r="E42" t="s">
         <v>360</v>
-      </c>
-      <c r="B42" t="s">
-        <v>361</v>
-      </c>
-      <c r="C42" t="s">
-        <v>362</v>
-      </c>
-      <c r="D42" t="s">
-        <v>363</v>
-      </c>
-      <c r="E42" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>362</v>
+      </c>
+      <c r="B43" t="s">
+        <v>363</v>
+      </c>
+      <c r="C43" t="s">
+        <v>364</v>
+      </c>
+      <c r="D43" t="s">
+        <v>365</v>
+      </c>
+      <c r="E43" t="s">
         <v>366</v>
       </c>
-      <c r="B43" t="s">
+      <c r="F43" t="s">
         <v>367</v>
-      </c>
-      <c r="C43" t="s">
-        <v>368</v>
-      </c>
-      <c r="D43" t="s">
-        <v>369</v>
-      </c>
-      <c r="E43" t="s">
-        <v>370</v>
-      </c>
-      <c r="F43" t="s">
-        <v>371</v>
       </c>
     </row>
   </sheetData>

--- a/t.xlsx
+++ b/t.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Astra\Documents\projects\1644.icu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Astra\Documents\projects\1644.icu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD0B3BA-8B46-4071-98CD-42734798CC55}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC0B059-985B-4F8B-A28E-96571E375DC7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="29400" windowHeight="12640" tabRatio="351" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="29400" windowHeight="12636" tabRatio="351" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="年表" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="430">
   <si>
     <t>朝代</t>
   </si>
@@ -85,61 +85,6 @@
     <t>黄帝</t>
   </si>
   <si>
-    <t>黄帝纪年算法参考：黄帝纪年
-黄帝6438年更新：经AI核对本站历法，修正了纪年计算问题。本站将继续为黄帝纪年执规治历。
-本站所使用的黄帝纪年算法是全网首发。修改自github@Jea杨的农历算法。经过数次修缮，已能稳定运作。同时，黄帝纪年的RESTful API也即将上线，免费为全球所有网站提供以黄帝登基时间为基准、以华夏历法为依据的授时服务。
-下文转载自知乎作者“吉连”。
-20世纪初，报刊上讨论过“黄帝纪年”问题，如1903年的《黄帝魂》认为，“黄帝开国”是在公元前2711年；1903年的《苏报》认为是在公元前2491年；1905年的《民报》则认为是在公元前2698年。20世纪中叶，翦伯赞在《中外历史年表》中，将五帝和夏、商、周各帝王的年数加起来，从公元前841年往前推算得出，黄帝开始执政是在公元前2550年[1]。
-20世纪末，随着中国考古学的飞速发展，考古学界也对五帝时代进行了讨论。其主流观点是将龙山时代（公元前3000年至公元前2000年）视为“五帝时代”，与炎帝、黄帝、颛顼、帝喾、尧、舜活动的时代对应起来，不少学者将黄帝年代定为仰韶文化晚期到龙山时代早期（公元前3500至公元前2500年）。但许顺湛、黄怀信、陈连开等少数学者认为，炎黄时代与考古学上的仰韶文化（公元前5000年至公元前3000年）相对应。他们甚至明确指出，仰韶文化的半坡类型对应于炎帝文化，庙底沟类型对应于黄帝文化[2]，黄帝年代在仰韶文化中晚期[3]。这是根据各个考古学文化的特点来判定五帝活动的时代或对应的考古学文化，并由碳14测年数据来给出其年代框架。
-在世纪之交，由中华炎黄文化研究会发起编辑的八卷本《炎黄汇典》，成为研究炎黄二帝及其时代、历史和文化的工具书，其中第一卷“史籍卷”中摘选了古代典籍和传世文献中有关炎帝、黄帝的历史资料，包括大量有关黄帝年代的历法记录。这为用历法记录计算黄帝年代提供了新的可能性。
-这里，根据与黄帝相关的历法记录，利用高精度“瑞士星历表”（Swiss Ephemeris）软件来计算、分析和确定黄帝的历史年代。这些计算涉及到天文历法中的年月日干支、朔与节气的时刻以及日月五星的运动等。
-黄帝“迎日推策”之年代
-《史记》等史书记载：“黄帝得宝鼎宛朐，问于鬼臾区。区对曰：‘帝得宝鼎神策，是岁己酉朔旦冬至，得天之纪，终而复始。’于是黄帝迎日推策，后率二十岁得朔旦冬至，凡二十推，三百八十年，黄帝仙登于天。”这就是说，该年的冬至日同时也是朔日，其日干支为己酉。
-为了充分检验各种可能性，将计算的时间段设定为公元前5400年至公元前2000年。计算步骤如下：第一，根据太阳和月亮的黄经相等条件计算所有朔的时刻，并精确到分钟，时间为北京时间；第二，计算所有冬至的时刻，即太阳黄经为270度时所对应的时刻，同样精确到分钟；第三，确定冬至和朔日是同一天的日期，并且该日的干支为己酉。计算结果为：公元前4375年1月22日（丙寅年戊子月己酉日）、公元前3574年1月17日（丁亥年庚子月己酉日）和公元前2773年1月12日（戊申年壬子月己酉日）。
-颛顼的历法起始日为公元前2807年2月26日；颛顼生于约公元前2840年，逝于公元前2743年，在位时间约为公元前2820至公元前2743年。众所周知，五帝中的颛顼晚于黄帝年代，而在前述三个日期中，公元前2773年与颛顼的年代相重合，因此必须舍弃。这样，黄帝“迎日推策”的年代只需在公元前4375年和公元前3574年两者之间选择。
-黄帝作《调历》之年代
-《史记•索隐》记载：“《世本》及《律历志》：黄帝使羲和占日，常仪占月，臾区占星气，伶伦造律吕，大挠作甲子，隶首作算数；容成综此六术，而著《调历》。”又称：“唯黄帝及殷﹑周﹑鲁并建子为正”。而《后汉书》记载：“黄帝造历，元起辛卯。” 这些文献说明，黄帝《调历》始于某年子月的朔日，其日干支为辛卯。晋•皇甫谧在《帝王世纪》中说：“黄帝在位百年而崩，年百一十岁。”因此，黄帝作《调历》与黄帝“迎日推策”之间不会超过一百年。这样，在黄帝“迎日推策”年代附近两百年的时间范围内，于前面计算得到的所有朔日中寻找出子月（即包含节气冬至之月）朔的日干支为辛卯的所有日期，就可知道黄帝作《调历》的年代。
-若黄帝“迎日推策”的年代为公元前4375年，则在公元前4475年至公元前4275年之间，“子月辛卯朔”有两个日期：公元前4444年1月6日（丁巳年庚子月辛卯日）和公元前4377年1月15日（甲子年甲子月辛卯日）；若黄帝“迎日推策”的年代为公元前3574年，则在公元前3674年至公元前3474年之间，“子月辛卯朔”有四个日期：公元前3633年1月9日（戊子年壬子月辛卯日）、公元前3608年12月23日（甲寅年甲子月辛卯日）、公元前3576年1月9日（乙酉年丙子月辛卯日）和公元前3483年1月1日（戊午年壬子月辛卯日）。
-关于黄帝《调历》的资料还有宋•罗泌《路史》和清•吴成权《纲鉴易知录》的记载，他们称黄帝“以作《调历》，岁纪甲寅，日纪甲子”。但这种说法恐怕与《史记》“历术甲子篇”提到的“太初元年，岁名焉逢摄提格，月名毕聚，日得甲子，夜半朔旦冬至”有关，焉逢摄提格就是甲寅年，其实这只是司马迁心目中的《太初历》，而不是黄帝的《调历》。
-黄帝即位之年代
-关于黄帝即位的年代，元•释念常《佛祖历代通载》记载：“太史公史记称，黄帝三十八年，命风后定甲子”，而宋•刘恕《资治通鉴外纪》称“黄帝元年丁亥”。这说明黄帝即位于丁亥年，37年后（甲子年）定甲子、作《调历》，也就是黄帝作《调历》时为甲子年。
-在前述黄帝作《调历》的六个日期中，只有公元前4377年1月15日这个日期属于甲子年。这样，就可以唯一地确定黄帝《调历》始于公元前4377年1月15日，同时说明黄帝“迎日推策”的“己酉朔旦冬至”为公元前4375年1月22日。由此可知，黄帝即位于公元前4414年（丁亥年）。
-黄帝出生之年代
-依据宋• 张 君房的《云笈七签》记载的“帝年十五，心虑无所不通，乃受国于有熊，袭封君之地”。按黄帝即位于公元前4414年，则黄帝出生于公元前4428年（癸酉年）。
-《路史》罗苹注：“王冰序《宝椟记》云，黄帝以戊己日生，故以土王。《五行书》云，以戊子日生。”若按“建子”的定义，在公元前4428年里，日干支为戊子的日期有二月初二、四月初四、六月初五、八月初五、十月初六和 十二月初七 。
-民间传说黄帝出生于二月初二“龙抬头”之时。公元前4400年左右，在二月（即包含节气大寒之月）里，当太阳落山之时，东方苍龙七宿的第一宿角宿就升起在东方的地平线上，这就是民间所称的“龙抬头”。而在公元前4450年至公元前4350年的一百年间，仅有唯一的“ 二月初二 戊子日”，即公元前4428年2月8日（癸酉年 二月初二 戊子日），这便是黄帝的出生日期。
-黄帝杀蚩尤之年代
-《路史》称：黄帝“年三十七，戮蚩尤于中冀。于是炎帝诸侯咸进委命，乃即帝位，都彭城。王承填而土行，故色尚黄，而天下号之黄帝。”《云笈七签》记载：“帝以罚叛之功……于是诸侯咸尊轩辕为天子。帝以己酉岁立，承神农之后，火生土，帝以土德称王天下，号黄帝。”同时，唐•王瓘《广黄帝本行纪》也提到“自黄帝己酉岁”。这些记载表明黄帝在37岁时“杀蚩尤、王天下”，该年为己酉年。
-按照黄帝出生于公元前4428年，再加上36年，则黄帝“杀蚩尤、王天下”的年代为公元前4392年，同时该年恰好为己酉年。如此就进一步说明“黄帝《调历》始于公元前4377年1月15日”这个结论的正确性。
-在《云笈七签》中还记载：“帝起有熊之墟，自号黄帝。帝乃恭己下士，侧身修德，在位二十一年，而蚩尤肆孽。”由此可知，蚩尤起兵于黄帝21年，即公元前4394年（丁未年），而被黄帝杀于公元前4392年（己酉年）。
-黄帝祥瑞之年代
-《今本竹书纪年》记载：黄帝“二十年，景云见。以云纪官，有景云之瑞。赤方气与青方气相连，赤方中有两星，青方中有一星，凡三星，皆黄色，以天清明时见于摄提，名曰景星。”其他记载还有“时有景星出见，形如半月”（《帝王世纪》）和“《史记》曰，黄帝时景星见，形如半月，可以夜作”（《渊鉴类函》）。从有关记载看，这很可能是一次超新星爆发现象，因为公元1006年超新星，史书记载为“见大星，色黄”、“状如半月，有芒角，煌煌然可以鉴物”（《宋史》等）。景星见于黄帝20年，则为公元前4395年（丙午年）。
-《今本竹书纪年》中还有一条记载：黄帝“五十七年秋，七月庚申，凤鸟至，帝祭于洛水”。黄帝57年为公元前4358年，但无论按“建子”还是“建寅”计算，该年均无“七月庚申”这个日子。然而《帝王世纪》的记载是：“黄帝五十年，七月庚申，天下大雾，三日三夜，雾除，帝游洛水之上，大鱼负图而出，今《河图帝观篇》也。”按黄帝历法“建子”计算，即为公元前4365年8月8日（丙子年七月十三庚申日）。
-黄帝奏《咸池》之年代
-《吕氏春秋》记载：“昔黄帝令伶伦作为律……黄帝又命伶伦与荣援铸十二钟，以和五音，以施英韶，以仲春之月，乙卯之日，日在奎，始奏之，命之曰《咸池》”。而黄帝之乐《咸池》与天象有关。《乐叶图征》称：“黄帝乐曰《咸池》。《咸池》，五车天关也。”五车天关均是天上的星宿。《史记》记载：“西宫咸池，曰天五潢。五潢，五帝车舍。”《史记·正义》指出：“咸池三星，在五车中，天潢南，鱼鸟之所托也。”
-然而，由于岁差效应的影响，仲春时“日在奎”只能发生在东周及其以后，在6000年以前是不可能的，那时是“日在毕觜之间”。唐初的李淳风就认为“日在奎”是依据秦历改写的（见《路史》罗苹注），《吕氏春秋》记载的“仲春之月，日在奎，昏弧中，旦建星中”就说明了这一点。笔者猜测黄帝奏《咸池》时是“月在奎”，而在编写《吕氏春秋》时有人依据当时流行的《月令》而将其改为“日在奎”。
-如果黄帝奏《咸池》时是“月在奎”，同时是仲春月乙卯日。在公元前4414年（黄帝即位之年）至公元前4314年（黄帝在位百年）之间进行计算和寻找，可以确定为公元前4403年4月25日（戊戌年 四月廿六 乙卯日）、公元前4346年4月26日（乙未年 四月廿六 乙卯日）和公元前4336年5月3日（乙巳年 四月廿四 乙卯日）三个日期。
-由于多种文献记载黄帝奏《咸池》是在杀蚩尤之后，而在公元前4336年5月3日清晨时月亮又偏靠壁宿，因此笔者倾向认为，黄帝奏《咸池》的日期是公元前4346年4月26日。该日恰好是节气春分，为仲春之月的标志，于是“帝张《咸池》之乐于洞庭之野”（《庄子》）。在仲春乙卯日的清晨，一弯残月挂在奎宿的下方，天上的“咸池”即五车星宿刚刚升出东方的地平线。于是黄帝将乐曲命名为《咸池》，而“仲春乙卯”这个特殊的日子也就流传下来了。
-然而“月在奎”只是笔者的假设。若不是“月在奎”，则黄帝奏《咸池》的年代就宽泛多了，数年内就会遇到一次“仲春月乙卯日”。而在公元前4000年至公元前5000年的时间段里，在仲春时节（即包含节气春分之月）的清晨，均可看到“五车天关”等星宿从东方的地平线升起。
-黄帝辞世之年代
-《路史》记载：黄帝“八月既望，鼎成死焉”，该书罗苹注“《五行书》帝以甲戍日崩，一云戊午”。这说明黄帝辞世于“八月既望”，日干支为甲戍或戊午。按王国维的“月相四分说”，既望为十五六日以后至廿二三日。“夏商周断代工程”的定义为“既望：满月后月的光面尚未显著亏缺”，在其推定的西周金文历谱中的既望对应着从十六日到廿三日。依据既望的这种定义，并按“建子”的八月为未月（即包含节气大暑之月），在黄帝在位50年至100年之间进行查找，其结果如下：若日干支为甲戍，则有公元前4356年、4346年、4341年、4335年、4330年和4320年等六个年代；若日干支为戊午，则有公元前4359年、4358年、4348年、4333年、4327年和4322年等六个年代。若按张闻玉等的“月相定点说”，既望为十六日，则黄帝辞世于公元前4341年8月16日（庚子年八月十六甲戍日）或是公元前4359年9月4日（壬午年八月十六戊午日）。
-关于黄帝的岁数或在位年数，在古代是众说纷纭。黄帝的在位年数有58年（《列子》）、78年（《路史》注）、100年（《博物志》和《帝王世纪》）、110年（《资治通鉴外纪》和《通志》）等说法，黄帝的岁数有110岁（《帝王世纪》等）和117岁（《路史》）等说法。如果这些说法中的数字是准确的话，则与上述“八月既望”的甲戍日或戊午日均不相合。如果这些数字是近似的，则会有多种年代的选择。
-《列子》记载：“黄帝即位十有五年，喜天下戴己……又十有五年，忧天下之不治……又二十有八年，天下大治，几若华胥氏之国，而帝登假，百姓号之，二百余年不辍。”这说明黄帝在位58年，因而黄帝辞世于公元前4357年，其年黄帝72岁，但该年不符合“八月既望”甲戍日或戊午日。如果黄帝奏《咸池》的时间确实是在公元前4346年，且《列子》所记载的并不是从黄帝即位于有熊国算起，而是从黄帝“王天下”算起，那么，黄帝辞世的日期是公元前4335年9月14日（丙午年 八月廿二 甲戍日），其时黄帝94岁、在位80年。
-黄帝年代之置信程度
-通过以上计算和分析，可列出黄帝大事年表。根据文献资料的可靠性及各年代间的一致性，还可大致判定各个年代的置信程度。
-置信程度最低的是黄帝辞世的年代，依据现有的资料尚无法得出一个可信的年代来。有关黄帝祥瑞和奏《咸池》的年代，置信程度也相对较低，这是由于文献的可靠性或相应记载有问题（如“日在奎”）而造成的。然而，关于黄帝出生、即位和杀蚩尤等年代的历法信息虽较为晚出，但计算出的相关年代却是相互一致的，说明这些信息可能是通过传承而保留下来的，因此这些年代具有相当的可靠性。同时，比较可靠的是黄帝作《调历》的年代，这是由于《后汉书》等史书记载的黄帝历法信息应该是准确的。
-置信程度最高的是黄帝“迎日推策”的年代，因为从《史记》开始，很多史书均有类似记载。依据“己酉朔旦冬至”确定的黄帝年代是在公元前4375年或公元前3574年附近，若考虑其他文献资料或考古学的证据，就能确定出黄帝年代是在公元前4375年左右。
-《史记》：己酉朔旦冬至。依据黄帝生年，可推算出黄帝甲子年为公元前4377年，以此也映证黄帝调历在公元前4377年1月15日（甲子年甲子月辛卯日）。
-综上所述：
-黄帝出生于公元前4428年2月8日（黄帝纪年前52年癸酉年二月初二戊子日），黄帝即位于前4414年，辞世于公元前4335年9月14日（丙午年 八月廿二 甲戍日），其时黄帝94岁、在位80年。
-基于回溯性纪年，历法向反方向推演得出黄帝调历在公元前4377年1月15日（甲子年甲子月辛卯日）
-由此可知中华民族始有统一的原始形态国家已经有6000余年的历史，而黄帝之前的神农氏已有四千年历史，中国人文历史始于万年之前的神农氏发明陶文天干时期。
-尽管考古学界普遍认为五帝时代为龙山时代，炎黄年代距今5000年左右，但尚未见到有人结合考古学文化与文献资料来做深入具体的研究。与之相反，虽然“五帝时代要上延至仰韶时代、炎黄的历史文化应与仰韶文化相关”只是少数学者的认识，但他们是将考古学文化与文献资料结合起来进行研究论证的。现在，依据古代文献中有关黄帝年代的历法记录来进行计算分析，认为黄帝的年代应该始于仰韶文化前期，而这与考古学结合其他文献研究得出的结论相一致。</t>
-  </si>
-  <si>
-    <t>少昊</t>
-  </si>
-  <si>
     <t>颛顼</t>
   </si>
   <si>
@@ -147,9 +92,6 @@
   </si>
   <si>
     <t>帝挚</t>
-  </si>
-  <si>
-    <t>帝挚因不善政被废</t>
   </si>
   <si>
     <t>陶唐</t>
@@ -250,9 +192,6 @@
   </si>
   <si>
     <t>隋朝</t>
-  </si>
-  <si>
-    <t>暂时将隋唐合并</t>
   </si>
   <si>
     <t>唐朝</t>
@@ -401,22 +340,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>榆罔</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>炎帝</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>首任炎帝（神农氏）石年登基，传8代，共520年</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>先神农</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>伏羲氏</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -449,18 +376,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>画八卦、定嫁娶、作甲子·《易·系辞》《帝王世纪》，这时候已经出现高度抽象的符号系统，伏羲和女娲是共治天下的。</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>开天辟地·《三五历纪》《路史·前纪一》，没有具体记载盘古作为帝王在位了多久</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>第八代炎帝，与黄帝战于阪泉、后结盟共伐蚩尤，在位33年，共同推举黄帝为帝</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>五龙氏</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -469,14 +384,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>传五十九姓，而非五十九世，具体的世数不详。</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>皇伯、皇仲、皇叔、皇季、皇少（五龙氏，分治五方），没有写世代数，默认我就写2000</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>合雒纪</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -497,68 +404,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>龙图腾、龙师、历象·《左传·昭17》《路史·前纪六》，太昊是东夷族，有可能就是华夏先祖，他是风姓，跟伏羲一脉相承。龙图腾首次出现。	
-太昊伏羲氏·女娲氏（女皇）·柏皇氏·中央氏·大庭氏·栗陆氏（昆连氏/骊连氏）·赫胥氏·葛天氏·尊卢氏·昊英氏·朱襄氏·阴康氏（阴符氏）·无怀氏·史皇氏（仓颉）·祝融氏（祝诵氏）·炎帝神农氏（轩辕号有时列此纪前，罗泌以黄帝属下一纪），共16～19氏</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>构木为巢避禽兽·《庄子·盗跖》《帝王世纪》，又称为大巢氏。有巢和燧人氏都在这一期
-十三氏·多世 辰放氏（始教衣皮）→蜀山氏→豗傀氏（浑敦别号之一）→东户氏→皇覃氏→启统氏→吉夷氏→几蘧氏→狶韦氏（豨韦氏）→大巢氏（有巢氏）→燧人氏→庸成氏（部分版本次序微异，有混沌氏列此纪）</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>传三姓（或四世），无具体氏号留传，教穴居乘蜚鹿</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>传六姓，无名号留传，乘蜚麟以理</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>传四姓，无名号留传，叙寿命记世系</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>分九州、始有君长·《命历序》"人皇九头百五十世"，总共九人，150世，我暂时算作1500年</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>对应的历史事件（当前历法）</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>二十二氏·六十余世 巨灵氏（钜灵氏）→句彊氏（句强氏）→谯明氏→涿光氏→钩陈氏（钩阵氏）→黄神氏（駏神氏前）→犭巨神氏（拒神氏/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="SimSun-ExtB"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>𤝙</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>神氏）→犁灵氏→大騩氏（大隗氏）→鬼騩氏（鬼隗氏）→弇兹氏（掩兹氏）→泰逢氏（泰逄氏）→冉相氏→盖盈氏→大敦氏→云阳氏（灵阳氏）→巫常氏→泰壹氏（泰一氏）→空桑氏→神民氏→倚帝氏（猗帝氏）→次民氏（次是氏）（共22氏，前后相继）</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>柏皇·赫胥·葛天·阴康·朱襄·无怀等，制乐舞、教耕织、治疾·《路史·因提纪》.太昊-神农在路史里是写在一起的</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>从黄帝开始 传位和在位相关信息开始变得明确了</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -1462,271 +1312,387 @@
     <t>（美洲：1492哥伦布→西班牙征服 Aztec（1519–1521）&amp; Inca（1532–1572）→三角贸易与种植园奴隶制；北美13州独立（1776）→美利坚宪法（1787）→19c西进与内战（1861–65）前奏在</t>
   </si>
   <si>
-    <t>对应的历史事件（按新推算）
-东亚	西亚	欧洲	美洲	其他</t>
+    <t>公元1847年 → 公元1912年</t>
+  </si>
+  <si>
+    <t>（晚清：太平天国（1851–1864）席卷半壁江山；第二次鸦片战争（1856–1860）与北京圆明园劫毁；洋务运动（1861起）办工厂/海军/学堂；甲午战争（1894–1895）惨败、马关条约割台赔款；戊戌变法（1898）百日而终；义和团（1899–1901）与八国联军；清末新政（1901–1911）立宪、练新军、废科举；1911辛亥革命，1912中华民国成立，溥仪退位）</t>
+  </si>
+  <si>
+    <t>（西亚：奥斯曼坦志麦特改革（Tanzimat，1839–1876）试图西化集权；苏伊士运河通航（1869）使埃及成英法争夺焦点；1881–1899 法国、意大利、英国相继侵占北非（突尼斯、利比亚、埃及）；波斯卡扎尔王朝沦为英俄缓冲区；1908青年土耳其革命推翻苏丹专制；阿拉伯民族主义与锡安主义在巴勒斯坦开始抬头）</t>
+  </si>
+  <si>
+    <t>（欧洲：1848革命浪潮席卷多国（法、德、奥、意）；1861意大利统一完成；1871德意志统一（普法战争、凡尔赛称帝）；1870–1914第二次工业革命：电力、内燃机、化学工业、钢铁、垄断资本；马克思《资本论》第一卷（1867）；1871巴黎公社；1904–1905日俄战争在欧洲舆论场引发震动；1912巴尔干战争削弱奥斯曼在欧洲残余）</t>
+  </si>
+  <si>
+    <t>（美洲：美国南北战争（1861–1865）废除奴隶制、联邦巩固；西进运动与印第安战争基本完成（1890伤膝河）；美西战争（1898）夺古巴/波多黎各/菲律宾，成太平洋—加勒比帝国；拉丁美洲：考迪罗（Caudillo）军阀循环、咖啡/牛肉/矿产出口经济依附欧美资本；巴西废除奴隶制（1888）、建立共和国（1889）；墨西哥迪亚斯独裁（1876–1911）现代化与农民不满并存）</t>
+  </si>
+  <si>
+    <t>（其他：日本明治维新（1868起）废藩置县、殖产兴业、征韩论与甲午/日俄胜利；印度1857兵变后由东印度公司统治转为英王直辖（1876维多利亚女皇头衔）；非洲：柏林会议（1884–1885）瓜分非洲，刚果自由邦、南非英布战争（1899–1902）；东南亚：英法荷殖民深化（越南、暹罗缓冲国、荷属东印度）；全球金本位、海底电缆、远洋轮船、世界时间（格林尼治标准时）一体化）</t>
+  </si>
+  <si>
+    <t>曾仕强也不敢明着跟满清势力作对，他是销售额最高的华人讲师。他曾经提到，很多神仙和历代皇帝都转世了，包括崇祯皇帝。因为这个时代不搏一搏将是万劫不复。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>曾仕强说老人不会老，小孩长不大，暗指人口贩卖产业提取干细胞</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>满系艺人给东南亚犯罪集团祝寿和贺新年，后来很多声音洗地。那里简直就是托克所的延续</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>西方人喜欢讲屠龙，屠龙以后会爆金币，指的可能就是消灭中国</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>万里长城在欧洲也有，它不是防御工事而是军用高速公路，古代中国可能占领着整个亚欧大陆</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>瑞士，意大利都有很多榫卯老房子，永济桥那样的桥，很可能是华人聚集地</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>英文发音很多跟客家话粤语相似，很可能来源于汉语</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>很多人鼓吹佳绒语是古汉语</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>实际客家话和粤语才是古汉语，没那么难懂</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>土木堡可能在德国，很多当前的地名可能在欧洲，被人故意篡改到东亚</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>《路史》里的东西被刻意淡化了，信史不信，而去信西方伪史。上古就有很灿烂的文明</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>周礼记载的国家机关复杂度不亚于今日，也许版图远超认知</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>潮汕信仰太阳公是崇祯，他可能并不是上吊而是战死</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>永久残疾性质的裹脚是清朝产物，满清牵强附会地伪造魏晋时期就有裹脚</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>猎巫行动专门谋害懂草药，给人治病的所谓女巫可能是残留华夏子民</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>耶稣可能是崇祯，他们的年龄，遇害时间都很相似，生日甚至同一天</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>西方强调古埃及文明的灿烂，摩亨佐这种都拉出来</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>为了掩盖中华文明的灿烂</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>满清托克所，柳叶边城墙，人口贩卖，系统性地消灭各族人口（航海日志）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>解手可能来自于托克所里的华人奴隶要绑手，上厕所才解开</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>汗衫实际是汉衫。穿在里面，汉人在满清只有婴儿襁褓和寿衣允许使用汉服</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿汉服的干尸“黄拙吾”意为皇出吾。此人六根脚趾，是洪承畴，海宁洪氏取代了满清皇族</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>真康熙病死，归来太高，是假冒的，换了种，满语不会讲</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>满清有多次换种，奴儿哈只血统早已失传</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>从雕塑艺术来看，满清憎恨烈士，汉人，明臣，美化洪承畴，说明甩不掉他</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>皇台吉承认用心理战让崇祯杀袁崇焕，实则可能反过来，袁确实反叛。是为了丑化明廷</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>满清修明史写崇祯凌迟处死袁，实则满清十大酷刑是清朝才有</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>EXO首期四个华人，分别代表着官-鹿晗，富-黄子韬，芒果系-张艺兴，满系-吴亦凡（高奢）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>清华大学就是清+华，是美国用满清赔款捐赠。清华美院屁股尤其歪</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>法国铁面人为明太子朱慈烺，在他之后西方迅速崛起</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>满清八旗对应着北欧8国，颜色高度相似。北欧是反华大本营</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛的作品可能被篡改，例如批判大汉族主义等言论，没有交叉证明记录，仅有文章</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛，周可能被毒害，身体本来硬朗，差不多同一时间急转直下，而且都是癌症</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>孙文说革命尚未成功，毛主席也称辛亥革命没有完成，只能用人民英雄纪念碑表达立场</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>建国后需要钱，可能满遗打钱了，溥仪不处死可以理解，后来还当政协委员有点过头</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>多个叛党叛国的满族人，百度百科被改成汉族</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>创办皇汉网，宣传极端言论的是满族人</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>满遗曾经搞复辟运动，遭到打击但可能不够彻底</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>华伦天奴创始人家里放很多满清画，估计是满清后裔。高奢品牌都搞丑化华人那一套</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>满遗热衷于满语复兴，颁金节等，高奢广告多推行以满代华，让汉服变和服。实则旗袍马褂瓜皮帽并非汉服而是满服</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>厂字领蜈蚣扣的满服跟俄罗斯布里亚特族完全一样。这是蒙古的一支，意为“森林的”</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>印尼人和满人有吃人传统，故朊病毒抗体高，白人也偏高。实锤其南下边打边吃的做法，史上最惨烈</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>实录记载满清部队据守城市被明军围困，最终吃光城中人而全灭。明军找出堆积如山的切了不要的女性阴部数吨</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>布里亚特篡夺女真族，改名满洲，改名满族。改金国为清国。之前，女真族已经基本汉化（完颜系）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>国内有巨大成吉思汗雕像，还有许多美化努尔哈只，施琅等汉奸的雕像，一定程度上说明他们的自身认知</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>满遗似乎认古中山国（白狄）为远祖，以蒙古为先祖，以奴儿哈只为先祖，并有三叉戟作为他们的标识</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>新华字典旧版“旗”的组词为五星红旗。新版为 八旗，并有相关注释</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>改开前教科书为丰子恺定版，插画漂亮。后面越改越歪，直至“毒教材”。领导留言板直接下架教育部投诉入口</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>宣扬黑人入华，难民入华的活动家与犹太人关系深，意图破坏所有纯净血统的凝聚力，因为犹太吃过这个亏（德三）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>日本有爱新觉罗社，满系与“瑞穗”家族关系大，满洲国为日本扶持，溥仪曾投靠日本</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>溥仪的哥哥爱新觉罗宪军主导参与731事件，日，满，犹太可能深度合作</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>非典，新冠可能均为投毒，明末鼠疫可能是投毒，因为疫情发展与战事完全吻合</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>有网友录视频说日本人满人在国内非常多通婚和聚居，可能与日本人学校有关</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>其实真正的满族只有爱新觉罗，其他都是女真族，例如钮钴禄氏，叶赫那拉</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>改开后出现一批满系艺人，如那英，新生代娱乐圈基本不再有满系</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>鹿晗关晓彤分手，很可能因为鹿晗属于官二代，而关晓彤属于满系艺人</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>达芬奇等许多西方科学家艺术家，都说是做梦的时候找到灵感，发明了xx。而且他们都没有后代，可能是翻译永乐大典的知识</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>文化战强度很高，你说永乐大典里有科技，水军就说里面有光刻机，纯串</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据中药材考证，某些药材像欧洲植物，佐证我们曾经有更大领土</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>今玉门关 铁门关 周围一马平川的戈壁，压根没鸟用。实际玉门关在匈牙利，铁门关在欧洲的铁门国家公园。隋朝挖的运河在欧洲</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂时将隋唐合并，推测为与宋并列的胡汉混合政权（陇东集团）而宋可能是纯汉人集团</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>公元1847年 → 公元1912年</t>
-  </si>
-  <si>
-    <t>（晚清：太平天国（1851–1864）席卷半壁江山；第二次鸦片战争（1856–1860）与北京圆明园劫毁；洋务运动（1861起）办工厂/海军/学堂；甲午战争（1894–1895）惨败、马关条约割台赔款；戊戌变法（1898）百日而终；义和团（1899–1901）与八国联军；清末新政（1901–1911）立宪、练新军、废科举；1911辛亥革命，1912中华民国成立，溥仪退位）</t>
-  </si>
-  <si>
-    <t>（西亚：奥斯曼坦志麦特改革（Tanzimat，1839–1876）试图西化集权；苏伊士运河通航（1869）使埃及成英法争夺焦点；1881–1899 法国、意大利、英国相继侵占北非（突尼斯、利比亚、埃及）；波斯卡扎尔王朝沦为英俄缓冲区；1908青年土耳其革命推翻苏丹专制；阿拉伯民族主义与锡安主义在巴勒斯坦开始抬头）</t>
-  </si>
-  <si>
-    <t>（欧洲：1848革命浪潮席卷多国（法、德、奥、意）；1861意大利统一完成；1871德意志统一（普法战争、凡尔赛称帝）；1870–1914第二次工业革命：电力、内燃机、化学工业、钢铁、垄断资本；马克思《资本论》第一卷（1867）；1871巴黎公社；1904–1905日俄战争在欧洲舆论场引发震动；1912巴尔干战争削弱奥斯曼在欧洲残余）</t>
-  </si>
-  <si>
-    <t>（美洲：美国南北战争（1861–1865）废除奴隶制、联邦巩固；西进运动与印第安战争基本完成（1890伤膝河）；美西战争（1898）夺古巴/波多黎各/菲律宾，成太平洋—加勒比帝国；拉丁美洲：考迪罗（Caudillo）军阀循环、咖啡/牛肉/矿产出口经济依附欧美资本；巴西废除奴隶制（1888）、建立共和国（1889）；墨西哥迪亚斯独裁（1876–1911）现代化与农民不满并存）</t>
-  </si>
-  <si>
-    <t>（其他：日本明治维新（1868起）废藩置县、殖产兴业、征韩论与甲午/日俄胜利；印度1857兵变后由东印度公司统治转为英王直辖（1876维多利亚女皇头衔）；非洲：柏林会议（1884–1885）瓜分非洲，刚果自由邦、南非英布战争（1899–1902）；东南亚：英法荷殖民深化（越南、暹罗缓冲国、荷属东印度）；全球金本位、海底电缆、远洋轮船、世界时间（格林尼治标准时）一体化）</t>
-  </si>
-  <si>
-    <t>（西汉建立：刘邦称帝（前202）→文景之治；七国之乱（前154）→汉武帝：推恩令/盐铁专卖/独尊儒术/击匈奴/丝绸之路凿空（张骞）；王莽篡汉（AD 9）→光武中兴）</t>
+    <t>商汤~商纣 小河沿文化</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>曾仕强也不敢明着跟满清势力作对，他是销售额最高的华人讲师。他曾经提到，很多神仙和历代皇帝都转世了，包括崇祯皇帝。因为这个时代不搏一搏将是万劫不复。</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>曾仕强说老人不会老，小孩长不大，暗指人口贩卖产业提取干细胞</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>满系艺人给东南亚犯罪集团祝寿和贺新年，后来很多声音洗地。那里简直就是托克所的延续</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>西方人喜欢讲屠龙，屠龙以后会爆金币，指的可能就是消灭中国</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>万里长城在欧洲也有，它不是防御工事而是军用高速公路，古代中国可能占领着整个亚欧大陆</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>瑞士，意大利都有很多榫卯老房子，永济桥那样的桥，很可能是华人聚集地</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>英文发音很多跟客家话粤语相似，很可能来源于汉语</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>很多人鼓吹佳绒语是古汉语</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>实际客家话和粤语才是古汉语，没那么难懂</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>土木堡可能在德国，很多当前的地名可能在欧洲，被人故意篡改到东亚</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>《路史》里的东西被刻意淡化了，信史不信，而去信西方伪史。上古就有很灿烂的文明</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>周礼记载的国家机关复杂度不亚于今日，也许版图远超认知</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>潮汕信仰太阳公是崇祯，他可能并不是上吊而是战死</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>永久残疾性质的裹脚是清朝产物，满清牵强附会地伪造魏晋时期就有裹脚</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>猎巫行动专门谋害懂草药，给人治病的所谓女巫可能是残留华夏子民</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>耶稣可能是崇祯，他们的年龄，遇害时间都很相似，生日甚至同一天</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>西方强调古埃及文明的灿烂，摩亨佐这种都拉出来</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>为了掩盖中华文明的灿烂</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>满清托克所，柳叶边城墙，人口贩卖，系统性地消灭各族人口（航海日志）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>解手可能来自于托克所里的华人奴隶要绑手，上厕所才解开</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>汗衫实际是汉衫。穿在里面，汉人在满清只有婴儿襁褓和寿衣允许使用汉服</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>穿汉服的干尸“黄拙吾”意为皇出吾。此人六根脚趾，是洪承畴，海宁洪氏取代了满清皇族</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>真康熙病死，归来太高，是假冒的，换了种，满语不会讲</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>满清有多次换种，奴儿哈只血统早已失传</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>从雕塑艺术来看，满清憎恨烈士，汉人，明臣，美化洪承畴，说明甩不掉他</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>皇台吉承认用心理战让崇祯杀袁崇焕，实则可能反过来，袁确实反叛。是为了丑化明廷</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>满清修明史写崇祯凌迟处死袁，实则满清十大酷刑是清朝才有</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>EXO首期四个华人，分别代表着官-鹿晗，富-黄子韬，芒果系-张艺兴，满系-吴亦凡（高奢）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>清华大学就是清+华，是美国用满清赔款捐赠。清华美院屁股尤其歪</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>法国铁面人为明太子朱慈烺，在他之后西方迅速崛起</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>满清八旗对应着北欧8国，颜色高度相似。北欧是反华大本营</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>毛的作品可能被篡改，例如批判大汉族主义等言论，没有交叉证明记录，仅有文章</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>毛，周可能被毒害，身体本来硬朗，差不多同一时间急转直下，而且都是癌症</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>孙文说革命尚未成功，毛主席也称辛亥革命没有完成，只能用人民英雄纪念碑表达立场</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>建国后需要钱，可能满遗打钱了，溥仪不处死可以理解，后来还当政协委员有点过头</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>多个叛党叛国的满族人，百度百科被改成汉族</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>创办皇汉网，宣传极端言论的是满族人</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>满遗曾经搞复辟运动，遭到打击但可能不够彻底</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>华伦天奴创始人家里放很多满清画，估计是满清后裔。高奢品牌都搞丑化华人那一套</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>满遗热衷于满语复兴，颁金节等，高奢广告多推行以满代华，让汉服变和服。实则旗袍马褂瓜皮帽并非汉服而是满服</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>厂字领蜈蚣扣的满服跟俄罗斯布里亚特族完全一样。这是蒙古的一支，意为“森林的”</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>印尼人和满人有吃人传统，故朊病毒抗体高，白人也偏高。实锤其南下边打边吃的做法，史上最惨烈</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>实录记载满清部队据守城市被明军围困，最终吃光城中人而全灭。明军找出堆积如山的切了不要的女性阴部数吨</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>布里亚特篡夺女真族，改名满洲，改名满族。改金国为清国。之前，女真族已经基本汉化（完颜系）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>国内有巨大成吉思汗雕像，还有许多美化努尔哈只，施琅等汉奸的雕像，一定程度上说明他们的自身认知</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>满遗似乎认古中山国（白狄）为远祖，以蒙古为先祖，以奴儿哈只为先祖，并有三叉戟作为他们的标识</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>新华字典旧版“旗”的组词为五星红旗。新版为 八旗，并有相关注释</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>改开前教科书为丰子恺定版，插画漂亮。后面越改越歪，直至“毒教材”。领导留言板直接下架教育部投诉入口</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>宣扬黑人入华，难民入华的活动家与犹太人关系深，意图破坏所有纯净血统的凝聚力，因为犹太吃过这个亏（德三）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>日本有爱新觉罗社，满系与“瑞穗”家族关系大，满洲国为日本扶持，溥仪曾投靠日本</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>溥仪的哥哥爱新觉罗宪军主导参与731事件，日，满，犹太可能深度合作</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>非典，新冠可能均为投毒，明末鼠疫可能是投毒，因为疫情发展与战事完全吻合</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>有网友录视频说日本人满人在国内非常多通婚和聚居，可能与日本人学校有关</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>其实真正的满族只有爱新觉罗，其他都是女真族，例如钮钴禄氏，叶赫那拉</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>改开后出现一批满系艺人，如那英，新生代娱乐圈基本不再有满系</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>鹿晗关晓彤分手，很可能因为鹿晗属于官二代，而关晓彤属于满系艺人</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>达芬奇等许多西方科学家艺术家，都说是做梦的时候找到灵感，发明了xx。而且他们都没有后代，可能是翻译永乐大典的知识</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>文化战强度很高，你说永乐大典里有科技，水军就说里面有光刻机，纯串</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>根据中药材考证，某些药材像欧洲植物，佐证我们曾经有更大领土</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>今玉门关 铁门关 周围一马平川的戈壁，压根没鸟用。实际玉门关在匈牙利，铁门关在欧洲的铁门国家公园。隋朝挖的运河在欧洲</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>中原腹地出现了规模宏大的环壕聚落和城池（如巩义双槐树遗址、襄汾陶寺遗址、神木石峁遗址等），出现了气势恢宏的宫墙和“前朝后寝”的布局</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>尧</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>舜</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>禹~启~夏桀 对应马家窑文化早期 马家浜文化。禹在位45年去世，传位给启</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄嚣</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>高阳，黄帝之孙，昌意之子</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙图腾、龙师、历象·《左传·昭17》《路史·前纪六》，太昊发源于东部，风姓，跟伏羲一脉相承。以龙纪官，龙图腾首次出现。太昊与伏羲应为不同的人，但承上启下，都以龙纪官，许多记载证明太昊比伏羲略早，故我们认定伏羲即位时可能尊太昊为高祖，或太昊为伏羲的前一代帝王</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>构木为巢避禽兽·《庄子·盗跖》《帝王世纪》，又称为大巢氏。有巢和燧人氏都在这一期
+辰放氏（皇次屈）：传4世 蜀山氏：传6世 豗傀氏：传6世 浑沌氏：传7世 东户氏：传17世 皇覃氏：传7世 启统氏：传3世 吉夷氏：传4世 儿蘧氏：传1世 猪韦氏：传4世 有巢氏：传2世 燧人氏（遂皇氏）：传4世 庸成氏：传8世。总共68世</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>华夏先民穴居。二十二氏·六十余世 巨灵氏（钜灵氏）→句彊氏（句强氏）→谯明氏→涿光氏→钩陈氏（钩阵氏）→黄神氏（駏神氏前）→犭巨神氏（拒神氏/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="SimSun-ExtB"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>𤝙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>神氏）→犁灵氏→大騩氏（大隗氏）→鬼騩氏（鬼隗氏）→弇兹氏（掩兹氏）→泰逢氏（泰逄氏）→冉相氏→盖盈氏→大敦氏→云阳氏（灵阳氏）→巫常氏→泰壹氏（泰一氏）→空桑氏→神民氏→倚帝氏（猗帝氏）→次民氏（次是氏）（共22氏，前后相继）
+泰一很可能就是东皇太一，则这时候政治中心可能在南方</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>传四姓，无名号留传，《盘古王表》记载“叙命纪传四世”</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>传六姓，无名号留传，乘蜚麟以理。同理，故写成6世</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>提挺氏生子三十五世，通纪七十二姓。可能是生35子。分化成35个部落，其子通氏得位，代数未详。
+推测这不是大一统的王朝，或提挺氏统一后又进行分封。可能是与周边部族逐渐融合，大家又自立门户，所以产生大量姓氏（72指多数）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>皇伯、皇仲、皇叔、皇季、皇少（五龙氏，分治五方）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>开天辟地·《三五历纪》《路史·前纪一》。黄帝内经记载上古之人能活到一百多岁，采纳此说法作为年份参考。伏羲女娲下半身是龙，头长有龙角，类似于神农氏的特征。可能早期中国人由龙演变而来。我认为五龙氏到天皇氏的历史确实有夸张成分，但可以作为个参考。我按照常规的帝王在位时间平均值推算年代 分为旧长度和新长度</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>首任帝（神农/炎帝石年）：在位140年 二任帝（临魁）：在位80年 三任帝（姜承/帝承）：在位60年 四任帝（姜明/帝明）：在位49年 五任帝（姜宜/帝直）：在位45年 六任帝（姜来/帝来）：在位48年 七任帝（姜克/帝哀）：在位43年 八任帝（榆罔/帝揄罔）：在位55年。总共520年。第八代炎帝与黄帝战于阪泉、后结盟共伐蚩尤，在位33年，共同推举黄帝为帝，黄河流域的仰韶文化、北方的红山文化、海岱地区的大汶口文化以及长江流域的大溪文化</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄帝娶西陵氏之女嫘祖为正妃，生下两个儿子：长子名为玄嚣（字青阳），也就是后来的少昊；次子名为昌意。我认为三皇五帝就是按时间顺序来的，而不是文化标识，是完全实际的。
+笔者认为三皇是太昊，伏羲，女娲；五帝是炎帝 黄帝 尧舜禹</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>帝喾是黄帝长子玄嚣的孙子</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>帝挚是帝喾的长子，禅让给帝尧</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>画八卦、定嫁娶、作甲子·《易·系辞》《帝王世纪》，这时候已经出现高度抽象的符号系统，伏羲和女娲共治天下，继位者：女娲氏（可能伏羲去世略早）、大庭氏、柏皇氏、中央氏、栗陆氏、骊连氏、混沌氏、赫胥氏、尊卢氏、昊英氏、有巢氏、朱襄氏、葛天氏、阴康氏、无怀氏。加上伏羲女娲总共17世。对应新石器晚期， 裴李岗文化 兴隆洼文化 大地湾文化 顶狮山文化  井头山遗址
+这里面还有一位有巢氏，古人认为是有巢氏的一支居住在陕西或者四川</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>今年</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄帝纪年算法参考：原文：huaxia.center  . 元年记为-1故在位80年记为81以便配平
+精准对应 重庆巫山大溪遗址（公元前4400年起）和山东泰安大汶口遗址（公元前4300年起）
+黄帝出生于公元前4428年2月8日（黄帝纪年前52年癸酉年二月初二戊子日），黄帝即位于前4414年，辞世于公元前4335年9月14日（丙午年 八月廿二 甲戍日），其时黄帝94岁、在位80年。
+基于回溯性纪年，历法向反方向推演得出黄帝调历在公元前4377年1月15日（甲子年甲子月辛卯日）
+由此可知中华民族始有统一的原始形态国家已经有6000余年的历史，而黄帝之前的神农氏已有四千年历史，中国人文历史始于万年之前的神农氏发明陶文天干时期。
+尽管考古学界普遍认为五帝时代为龙山时代，炎黄年代距今5000年左右，但尚未见到有人结合考古学文化与文献资料来做深入具体的研究。与之相反，虽然“五帝时代要上延至仰韶时代、炎黄的历史文化应与仰韶文化相关”只是少数学者的认识，但他们是将考古学文化与文献资料结合起来进行研究论证的。现在，依据古代文献中有关黄帝年代的历法记录来进行计算分析，认为黄帝的年代应该始于仰韶文化前期，而这与考古学结合其他文献研究得出的结论相一致。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1842,7 +1808,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1872,9 +1838,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2356,25 +2319,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:V44"/>
-  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L43"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="25.05" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.26953125" style="1" customWidth="1"/>
-    <col min="2" max="3" width="9.26953125" style="1"/>
-    <col min="4" max="4" width="9.26953125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7265625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.90625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.453125" style="1" customWidth="1"/>
-    <col min="9" max="10" width="11.81640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.08984375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="31.81640625" style="1" customWidth="1"/>
-    <col min="13" max="17" width="17.1796875" style="1" customWidth="1"/>
-    <col min="18" max="22" width="17.90625" style="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.26953125" style="1"/>
+    <col min="1" max="1" width="8.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="11.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="11.77734375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="38.21875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.21875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2411,467 +2372,348 @@
       <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-    </row>
-    <row r="2" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B2" s="3">
         <f t="array" ref="B2">C3</f>
-        <v>-19512</v>
+        <v>-68277279</v>
       </c>
       <c r="C2" s="3">
         <f t="array" ref="C2">B2-F2</f>
-        <v>-19512</v>
+        <v>-70977279</v>
       </c>
       <c r="D2" s="1">
         <f t="shared" ref="D2:D12" si="0">B2+4413</f>
-        <v>-15099</v>
+        <v>-68272866</v>
       </c>
       <c r="E2" s="1">
         <f t="shared" ref="E2:E12" si="1">C2+4413</f>
-        <v>-15099</v>
+        <v>-70972866</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>2700000</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
       </c>
       <c r="H2" s="1">
         <f t="array" ref="H2">I2-G2</f>
-        <v>-21466</v>
+        <v>-26534</v>
       </c>
       <c r="I2" s="1">
         <f t="array" ref="I2">H3</f>
-        <v>-21466</v>
+        <v>-26534</v>
       </c>
       <c r="J2" s="1">
-        <f t="shared" ref="J2:J12" si="2">H2+4413</f>
-        <v>-17053</v>
+        <f t="array" ref="J2">K2-G2</f>
+        <v>-22120</v>
       </c>
       <c r="K2" s="1">
-        <f t="shared" ref="K2:K12" si="3">I2+4413</f>
-        <v>-17053</v>
+        <f t="array" ref="K2">J3</f>
+        <v>-22120</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B3" s="3">
         <f t="array" ref="B3">C4</f>
-        <v>-17012</v>
+        <v>-16677279</v>
       </c>
       <c r="C3" s="3">
         <f t="array" ref="C3">B3-F3</f>
-        <v>-19512</v>
+        <v>-68277279</v>
       </c>
       <c r="D3" s="1">
         <f t="shared" si="0"/>
-        <v>-12599</v>
+        <v>-16672866</v>
       </c>
       <c r="E3" s="1">
         <f t="shared" si="1"/>
-        <v>-15099</v>
+        <v>-68272866</v>
       </c>
       <c r="F3" s="1">
-        <v>2500</v>
+        <v>51600000</v>
       </c>
       <c r="G3" s="1">
         <v>2500</v>
       </c>
       <c r="H3" s="1">
         <f t="array" ref="H3">I3-G3</f>
-        <v>-21466</v>
+        <v>-26534</v>
       </c>
       <c r="I3" s="1">
         <f t="array" ref="I3">H4</f>
-        <v>-18966</v>
+        <v>-24034</v>
       </c>
       <c r="J3" s="1">
-        <f t="shared" si="2"/>
-        <v>-17053</v>
+        <f t="array" ref="J3">K3-G3</f>
+        <v>-22120</v>
       </c>
       <c r="K3" s="1">
-        <f t="shared" si="3"/>
-        <v>-14553</v>
+        <f t="array" ref="K3">J4</f>
+        <v>-19620</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B4" s="3">
         <f t="array" ref="B4">C5</f>
-        <v>-15012</v>
+        <v>-12123279</v>
       </c>
       <c r="C4" s="3">
         <f t="array" ref="C4">B4-F4</f>
-        <v>-17012</v>
+        <v>-16677279</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" si="0"/>
-        <v>-10599</v>
+        <v>-12118866</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" si="1"/>
-        <v>-12599</v>
+        <v>-16672866</v>
       </c>
       <c r="F4" s="1">
-        <v>2000</v>
+        <v>4554000</v>
       </c>
       <c r="G4" s="1">
         <v>2000</v>
       </c>
       <c r="H4" s="1">
         <f t="array" ref="H4">I4-G4</f>
-        <v>-18966</v>
+        <v>-24034</v>
       </c>
       <c r="I4" s="1">
         <f t="array" ref="I4">H5</f>
-        <v>-16966</v>
+        <v>-22034</v>
       </c>
       <c r="J4" s="1">
-        <f t="shared" si="2"/>
-        <v>-14553</v>
+        <f t="array" ref="J4">K4-G4</f>
+        <v>-19620</v>
       </c>
       <c r="K4" s="1">
-        <f t="shared" si="3"/>
-        <v>-12553</v>
+        <f t="array" ref="K4">J5</f>
+        <v>-17620</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B5" s="3">
         <f t="array" ref="B5">C6</f>
-        <v>-13512</v>
+        <v>-8569279</v>
       </c>
       <c r="C5" s="3">
         <f t="array" ref="C5">B5-F5</f>
-        <v>-15012</v>
+        <v>-12123279</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>-9099</v>
+        <v>-8564866</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="1"/>
-        <v>-10599</v>
+        <v>-12118866</v>
       </c>
       <c r="F5" s="1">
-        <v>1500</v>
+        <v>3554000</v>
       </c>
       <c r="G5" s="1">
         <v>1500</v>
       </c>
       <c r="H5" s="1">
         <f t="array" ref="H5">I5-G5</f>
-        <v>-16966</v>
+        <v>-22034</v>
       </c>
       <c r="I5" s="1">
         <f t="array" ref="I5">H6</f>
-        <v>-15466</v>
+        <v>-20534</v>
       </c>
       <c r="J5" s="1">
-        <f t="shared" si="2"/>
-        <v>-12553</v>
+        <f t="array" ref="J5">K5-G5</f>
+        <v>-17620</v>
       </c>
       <c r="K5" s="1">
-        <f t="shared" si="3"/>
-        <v>-11053</v>
+        <f t="array" ref="K5">J6</f>
+        <v>-16120</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B6" s="3">
         <f t="array" ref="B6">C7</f>
-        <v>-12512</v>
+        <v>-3015279</v>
       </c>
       <c r="C6" s="3">
         <f t="array" ref="C6">B6-F6</f>
-        <v>-13512</v>
+        <v>-8569279</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="0"/>
-        <v>-8099</v>
+        <v>-3010866</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="1"/>
-        <v>-9099</v>
+        <v>-8564866</v>
       </c>
       <c r="F6" s="1">
-        <v>1000</v>
+        <v>5554000</v>
       </c>
       <c r="G6" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
         <f t="array" ref="H6">I6-G6</f>
-        <v>-15466</v>
+        <v>-20534</v>
       </c>
       <c r="I6" s="1">
         <f t="array" ref="I6">H7</f>
-        <v>-14466</v>
+        <v>-20434</v>
       </c>
       <c r="J6" s="1">
-        <f t="shared" si="2"/>
-        <v>-11053</v>
+        <f t="array" ref="J6">K6-G6</f>
+        <v>-16120</v>
       </c>
       <c r="K6" s="1">
-        <f t="shared" si="3"/>
-        <v>-10053</v>
+        <f t="array" ref="K6">J7</f>
+        <v>-16020</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B7" s="3">
         <f t="array" ref="B7">C8</f>
-        <v>-10512</v>
+        <v>-3014779</v>
       </c>
       <c r="C7" s="3">
         <f t="array" ref="C7">B7-F7</f>
-        <v>-12512</v>
+        <v>-3015279</v>
       </c>
       <c r="D7" s="1">
         <f t="shared" si="0"/>
-        <v>-6099</v>
+        <v>-3010366</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="1"/>
-        <v>-8099</v>
+        <v>-3010866</v>
       </c>
       <c r="F7" s="1">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="G7" s="1">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="H7" s="1">
         <f t="array" ref="H7">I7-G7</f>
-        <v>-14466</v>
+        <v>-20434</v>
       </c>
       <c r="I7" s="1">
         <f t="array" ref="I7">H8</f>
-        <v>-12466</v>
+        <v>-19934</v>
       </c>
       <c r="J7" s="1">
-        <f t="shared" si="2"/>
-        <v>-10053</v>
+        <f t="array" ref="J7">K7-G7</f>
+        <v>-16020</v>
       </c>
       <c r="K7" s="1">
-        <f t="shared" si="3"/>
-        <v>-8053</v>
+        <f t="array" ref="K7">J8</f>
+        <v>-15520</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B8" s="3">
         <f t="array" ref="B8">C9</f>
-        <v>-10112</v>
+        <v>-2563779</v>
       </c>
       <c r="C8" s="3">
         <f t="array" ref="C8">B8-F8</f>
-        <v>-10512</v>
+        <v>-3014779</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
-        <v>-5699</v>
+        <v>-2559366</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="1"/>
-        <v>-6099</v>
+        <v>-3010366</v>
       </c>
       <c r="F8" s="1">
-        <v>400</v>
+        <v>451000</v>
       </c>
       <c r="G8" s="1">
         <v>400</v>
       </c>
       <c r="H8" s="1">
         <f t="array" ref="H8">I8-G8</f>
-        <v>-12466</v>
+        <v>-19934</v>
       </c>
       <c r="I8" s="1">
         <f t="array" ref="I8">H9</f>
-        <v>-12066</v>
+        <v>-19534</v>
       </c>
       <c r="J8" s="1">
-        <f t="shared" si="2"/>
-        <v>-8053</v>
+        <f t="array" ref="J8">K8-G8</f>
+        <v>-15520</v>
       </c>
       <c r="K8" s="1">
-        <f t="shared" si="3"/>
-        <v>-7653</v>
+        <f t="array" ref="K8">J9</f>
+        <v>-15120</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="B9" s="3">
         <f t="array" ref="B9">C10</f>
-        <v>-9512</v>
+        <v>-2563179</v>
       </c>
       <c r="C9" s="3">
         <f t="array" ref="C9">B9-F9</f>
-        <v>-10112</v>
+        <v>-2563779</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>-5099</v>
+        <v>-2558766</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="1"/>
-        <v>-5699</v>
+        <v>-2559366</v>
       </c>
       <c r="F9" s="1">
         <v>600</v>
@@ -2881,58 +2723,43 @@
       </c>
       <c r="H9" s="1">
         <f t="array" ref="H9">I9-G9</f>
-        <v>-12066</v>
+        <v>-19534</v>
       </c>
       <c r="I9" s="1">
         <f t="array" ref="I9">H10</f>
-        <v>-11466</v>
+        <v>-18934</v>
       </c>
       <c r="J9" s="1">
-        <f t="shared" si="2"/>
-        <v>-7653</v>
+        <f t="array" ref="J9">K9-G9</f>
+        <v>-15120</v>
       </c>
       <c r="K9" s="1">
-        <f t="shared" si="3"/>
-        <v>-7053</v>
+        <f t="array" ref="K9">J10</f>
+        <v>-14520</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B10" s="3">
         <f t="array" ref="B10">C11</f>
-        <v>-9112</v>
+        <v>-2562779</v>
       </c>
       <c r="C10" s="3">
         <f t="array" ref="C10">B10-F10</f>
-        <v>-9512</v>
+        <v>-2563179</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
-        <v>-4699</v>
+        <v>-2558366</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
-        <v>-5099</v>
+        <v>-2558766</v>
       </c>
       <c r="F10" s="1">
         <v>400</v>
@@ -2942,241 +2769,181 @@
       </c>
       <c r="H10" s="1">
         <f t="array" ref="H10">I10-G10</f>
-        <v>-11466</v>
+        <v>-18934</v>
       </c>
       <c r="I10" s="1">
         <f t="array" ref="I10">H11</f>
-        <v>-11066</v>
+        <v>-18534</v>
       </c>
       <c r="J10" s="1">
-        <f t="shared" si="2"/>
-        <v>-7053</v>
+        <f t="array" ref="J10">K10-G10</f>
+        <v>-14520</v>
       </c>
       <c r="K10" s="1">
-        <f t="shared" si="3"/>
-        <v>-6653</v>
+        <f t="array" ref="K10">J11</f>
+        <v>-14120</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="V10" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B11" s="3">
         <f t="array" ref="B11">C12</f>
-        <v>-6112</v>
+        <v>-8779</v>
       </c>
       <c r="C11" s="3">
         <f t="array" ref="C11">B11-F11</f>
-        <v>-9112</v>
+        <v>-2562779</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>-1699</v>
+        <v>-4366</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>-4699</v>
+        <v>-2558366</v>
       </c>
       <c r="F11" s="1">
-        <v>3000</v>
+        <v>2554000</v>
       </c>
       <c r="G11" s="1">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="H11" s="1">
         <f t="array" ref="H11">I11-G11</f>
-        <v>-11066</v>
+        <v>-18534</v>
       </c>
       <c r="I11" s="1">
         <f t="array" ref="I11">H12</f>
-        <v>-8066</v>
+        <v>-12534</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" si="2"/>
-        <v>-6653</v>
+        <f t="array" ref="J11">K11-G11</f>
+        <v>-14120</v>
       </c>
       <c r="K11" s="1">
-        <f t="shared" si="3"/>
-        <v>-3653</v>
+        <f t="array" ref="K11">J12</f>
+        <v>-8120</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B12" s="3">
         <f t="array" ref="B12">C13</f>
-        <v>-4812</v>
+        <v>-3779</v>
       </c>
       <c r="C12" s="3">
         <f t="array" ref="C12">B12-F12</f>
-        <v>-6112</v>
+        <v>-8779</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
-        <v>-399</v>
+        <v>634</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="1"/>
-        <v>-1699</v>
+        <v>-4366</v>
       </c>
       <c r="F12" s="1">
-        <v>1300</v>
+        <v>5000</v>
       </c>
       <c r="G12" s="1">
-        <v>1300</v>
+        <v>6800</v>
       </c>
       <c r="H12" s="1">
         <f t="array" ref="H12">I12-G12</f>
-        <v>-8066</v>
+        <v>-12534</v>
       </c>
       <c r="I12" s="1">
         <f t="array" ref="I12">H13</f>
-        <v>-6766</v>
+        <v>-5734</v>
       </c>
       <c r="J12" s="1">
-        <f t="shared" si="2"/>
-        <v>-3653</v>
+        <f t="array" ref="J12">K12-G12</f>
+        <v>-8120</v>
       </c>
       <c r="K12" s="1">
-        <f t="shared" si="3"/>
-        <v>-2353</v>
+        <f t="array" ref="K12">J13</f>
+        <v>-1320</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="V12" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B13" s="3">
         <f t="array" ref="B13">C14</f>
-        <v>-4312</v>
+        <v>-3679</v>
       </c>
       <c r="C13" s="3">
         <f t="array" ref="C13">B13-F13</f>
-        <v>-4812</v>
+        <v>-3779</v>
       </c>
       <c r="D13" s="1">
-        <f t="shared" ref="D13:D14" si="4">B13+4413</f>
-        <v>101</v>
+        <f t="shared" ref="D13:D14" si="2">B13+4413</f>
+        <v>734</v>
       </c>
       <c r="E13" s="1">
-        <f t="shared" ref="E13:E14" si="5">C13+4413</f>
-        <v>-399</v>
+        <f t="shared" ref="E13:E14" si="3">C13+4413</f>
+        <v>634</v>
       </c>
       <c r="F13" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G13" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
         <f t="array" ref="H13">I13-G13</f>
-        <v>-6766</v>
+        <v>-5734</v>
       </c>
       <c r="I13" s="1">
         <f t="array" ref="I13">H14</f>
-        <v>-6266</v>
+        <v>-5634</v>
       </c>
       <c r="J13" s="1">
-        <f t="shared" ref="J13:J14" si="6">H13+4413</f>
-        <v>-2353</v>
+        <f t="array" ref="J13">K13-G13</f>
+        <v>-1320</v>
       </c>
       <c r="K13" s="1">
-        <f t="shared" ref="K13:K14" si="7">I13+4413</f>
-        <v>-1853</v>
+        <f t="array" ref="K13">J14</f>
+        <v>-1220</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="V13" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B14" s="3">
-        <f t="array" ref="B14">C15</f>
-        <v>-3612</v>
+        <f>C15</f>
+        <v>-2979</v>
       </c>
       <c r="C14" s="3">
         <f t="array" ref="C14">B14-F14</f>
-        <v>-4312</v>
+        <v>-3679</v>
       </c>
       <c r="D14" s="1">
-        <f t="shared" si="4"/>
-        <v>801</v>
+        <f t="shared" si="2"/>
+        <v>1434</v>
       </c>
       <c r="E14" s="1">
-        <f t="shared" si="5"/>
-        <v>101</v>
+        <f t="shared" si="3"/>
+        <v>734</v>
       </c>
       <c r="F14" s="1">
         <v>700</v>
@@ -3186,874 +2953,666 @@
       </c>
       <c r="H14" s="1">
         <f t="array" ref="H14">I14-G14</f>
-        <v>-6266</v>
+        <v>-5634</v>
       </c>
       <c r="I14" s="1">
-        <f t="array" ref="I14">H15</f>
-        <v>-5566</v>
+        <f>H15</f>
+        <v>-4934</v>
       </c>
       <c r="J14" s="1">
-        <f t="shared" si="6"/>
-        <v>-1853</v>
+        <f t="array" ref="J14">K14-G14</f>
+        <v>-1220</v>
       </c>
       <c r="K14" s="1">
-        <f t="shared" si="7"/>
-        <v>-1153</v>
+        <f t="array" ref="K14">J15</f>
+        <v>-520</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="V14" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B15" s="3">
         <f t="array" ref="B15">C16</f>
-        <v>-3012</v>
+        <v>-2459</v>
       </c>
       <c r="C15" s="3">
         <f t="array" ref="C15">B15-F15</f>
-        <v>-3612</v>
+        <v>-2979</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" ref="D15" si="8">B15+4413</f>
-        <v>1401</v>
+        <f t="shared" ref="D15" si="4">B15+4413</f>
+        <v>1954</v>
       </c>
       <c r="E15" s="1">
-        <f t="shared" ref="E15" si="9">C15+4413</f>
-        <v>801</v>
+        <f t="shared" ref="E15" si="5">C15+4413</f>
+        <v>1434</v>
       </c>
       <c r="F15" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
       <c r="G15" s="1">
-        <v>600</v>
+        <v>520</v>
       </c>
       <c r="H15" s="1">
         <f t="array" ref="H15">I15-G15</f>
-        <v>-5566</v>
+        <v>-4934</v>
       </c>
       <c r="I15" s="1">
         <f t="array" ref="I15">H16</f>
-        <v>-4966</v>
+        <v>-4414</v>
       </c>
       <c r="J15" s="1">
-        <f t="shared" ref="J15" si="10">H15+4413</f>
-        <v>-1153</v>
+        <f>K15-G15-1</f>
+        <v>-520</v>
       </c>
       <c r="K15" s="1">
-        <f t="shared" ref="K15" si="11">I15+4413</f>
-        <v>-553</v>
+        <f>J16</f>
+        <v>1</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>52</v>
+        <v>423</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B16" s="3">
-        <f t="array" ref="B16">C17</f>
-        <v>-2492</v>
+        <v>-2539</v>
       </c>
       <c r="C16" s="3">
-        <f t="array" ref="C16">B16-F16</f>
-        <v>-3012</v>
+        <v>-2459</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" ref="D16:D17" si="12">B16+4413</f>
-        <v>1921</v>
+        <f>B16+4413</f>
+        <v>1874</v>
       </c>
       <c r="E16" s="1">
-        <f t="shared" ref="E16:E17" si="13">C16+4413</f>
-        <v>1401</v>
+        <f>C16+4413</f>
+        <v>1954</v>
       </c>
       <c r="F16" s="1">
-        <v>520</v>
+        <v>80</v>
       </c>
       <c r="G16" s="1">
-        <v>520</v>
+        <v>80</v>
       </c>
       <c r="H16" s="1">
-        <f t="array" ref="H16">I16-G16</f>
-        <v>-4966</v>
+        <f>-4414</f>
+        <v>-4414</v>
       </c>
       <c r="I16" s="1">
-        <f t="array" ref="I16">H17</f>
-        <v>-4446</v>
+        <f t="array" ref="I16">H16+G16</f>
+        <v>-4334</v>
       </c>
       <c r="J16" s="1">
-        <f t="shared" ref="J16:J17" si="14">H16+4413</f>
-        <v>-553</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <f t="shared" ref="K16:K17" si="15">I16+4413</f>
-        <v>-33</v>
+        <f>J16+G16-1</f>
+        <v>80</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="V16" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>51</v>
+        <v>413</v>
       </c>
       <c r="B17" s="3">
         <v>-2459</v>
       </c>
       <c r="C17" s="3">
-        <f t="array" ref="C17">B17-F17</f>
-        <v>-2492</v>
+        <v>-2375</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="D17:D22" si="6">B17+4413</f>
         <v>1954</v>
       </c>
       <c r="E17" s="1">
-        <f t="shared" si="13"/>
-        <v>1921</v>
+        <f t="shared" ref="E17:E22" si="7">C17+4413</f>
+        <v>2038</v>
       </c>
       <c r="F17" s="1">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
-        <f t="array" ref="H17">I17-G17</f>
-        <v>-4446</v>
+        <f>I16</f>
+        <v>-4334</v>
       </c>
       <c r="I17" s="1">
-        <f t="array" ref="I17">H18</f>
-        <v>-4413</v>
+        <f t="array" ref="I17">H17+G17</f>
+        <v>-4334</v>
       </c>
       <c r="J17" s="1">
-        <f t="shared" si="14"/>
-        <v>-33</v>
+        <f t="array" ref="J17">K16</f>
+        <v>80</v>
       </c>
       <c r="K17" s="1">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="array" ref="K17">J17+G17</f>
+        <v>80</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="V17" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" s="3">
-        <v>-2559</v>
+        <v>-2375</v>
       </c>
       <c r="C18" s="3">
-        <v>-2459</v>
+        <v>-2297</v>
       </c>
       <c r="D18" s="1">
-        <f>B18+4413</f>
-        <v>1854</v>
+        <f t="shared" si="6"/>
+        <v>2038</v>
       </c>
       <c r="E18" s="1">
-        <f>C18+4413</f>
-        <v>1954</v>
+        <f t="shared" si="7"/>
+        <v>2116</v>
       </c>
       <c r="F18" s="1">
         <f t="array" ref="F18">C18-B18</f>
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="G18" s="1">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="H18" s="1">
-        <f t="array" ref="H18">I18-G18</f>
-        <v>-4413</v>
+        <f>I17</f>
+        <v>-4334</v>
       </c>
       <c r="I18" s="1">
-        <f t="array" ref="I18">H19</f>
-        <v>-4313</v>
+        <f t="array" ref="I18">H18+G18</f>
+        <v>-4256</v>
       </c>
       <c r="J18" s="1">
-        <f>H18+4413</f>
-        <v>0</v>
+        <f t="array" ref="J18">K17</f>
+        <v>80</v>
       </c>
       <c r="K18" s="1">
-        <f>I18+4413</f>
-        <v>100</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="U18" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="V18" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" ref="K18">J18+G18</f>
+        <v>158</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B19" s="3">
-        <v>-2459</v>
+        <v>-2297</v>
       </c>
       <c r="C19" s="3">
-        <v>-2375</v>
+        <v>-2227</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" ref="D19:D24" si="16">B19+4413</f>
-        <v>1954</v>
+        <f t="shared" si="6"/>
+        <v>2116</v>
       </c>
       <c r="E19" s="1">
-        <f t="shared" ref="E19:E24" si="17">C19+4413</f>
-        <v>2038</v>
+        <f t="shared" si="7"/>
+        <v>2186</v>
       </c>
       <c r="F19" s="1">
         <f t="array" ref="F19">C19-B19</f>
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="G19" s="1">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="H19" s="1">
-        <f t="array" ref="H19">I19-G19</f>
-        <v>-4313</v>
+        <f t="shared" ref="H19:H42" si="8">I18</f>
+        <v>-4256</v>
       </c>
       <c r="I19" s="1">
-        <f t="array" ref="I19">H20</f>
-        <v>-4229</v>
+        <f t="array" ref="I19">H19+G19</f>
+        <v>-4186</v>
       </c>
       <c r="J19" s="1">
-        <f t="shared" ref="J19:J24" si="18">H19+4413</f>
-        <v>100</v>
+        <f t="array" ref="J19">K18</f>
+        <v>158</v>
       </c>
       <c r="K19" s="1">
-        <f t="shared" ref="K19:K24" si="19">I19+4413</f>
-        <v>184</v>
+        <f t="array" ref="K19">J19+G19</f>
+        <v>228</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="V19" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="3">
-        <v>-2375</v>
+        <v>-2227</v>
       </c>
       <c r="C20" s="3">
-        <v>-2297</v>
+        <v>-2218</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" si="16"/>
-        <v>2038</v>
+        <f t="shared" si="6"/>
+        <v>2186</v>
       </c>
       <c r="E20" s="1">
-        <f t="shared" si="17"/>
-        <v>2116</v>
+        <f t="shared" si="7"/>
+        <v>2195</v>
       </c>
       <c r="F20" s="1">
         <f t="array" ref="F20">C20-B20</f>
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="G20" s="1">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="H20" s="1">
-        <f t="array" ref="H20">I20-G20</f>
-        <v>-4229</v>
+        <f t="shared" si="8"/>
+        <v>-4186</v>
       </c>
       <c r="I20" s="1">
-        <f t="array" ref="I20">H21</f>
-        <v>-4151</v>
+        <f t="array" ref="I20">H20+G20</f>
+        <v>-4177</v>
       </c>
       <c r="J20" s="1">
-        <f t="shared" si="18"/>
-        <v>184</v>
+        <f t="array" ref="J20">K19</f>
+        <v>228</v>
       </c>
       <c r="K20" s="1">
-        <f t="shared" si="19"/>
-        <v>262</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="V20" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" ref="K20">J20+G20</f>
+        <v>237</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B21" s="3">
-        <v>-2297</v>
+        <v>-2218</v>
       </c>
       <c r="C21" s="3">
-        <v>-2227</v>
+        <v>-2120</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" si="16"/>
-        <v>2116</v>
+        <f t="shared" si="6"/>
+        <v>2195</v>
       </c>
       <c r="E21" s="1">
-        <f t="shared" si="17"/>
-        <v>2186</v>
+        <f t="shared" si="7"/>
+        <v>2293</v>
       </c>
       <c r="F21" s="1">
         <f t="array" ref="F21">C21-B21</f>
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="G21" s="1">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="H21" s="1">
-        <f t="array" ref="H21">I21-G21</f>
-        <v>-4151</v>
+        <f t="shared" si="8"/>
+        <v>-4177</v>
       </c>
       <c r="I21" s="1">
-        <f t="array" ref="I21">H22</f>
-        <v>-4081</v>
+        <f t="array" ref="I21">H21+G21</f>
+        <v>-4079</v>
       </c>
       <c r="J21" s="1">
-        <f t="shared" si="18"/>
-        <v>262</v>
+        <f t="array" ref="J21">K20</f>
+        <v>237</v>
       </c>
       <c r="K21" s="1">
-        <f t="shared" si="19"/>
-        <v>332</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="V21" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" ref="K21">J21+G21</f>
+        <v>335</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B22" s="3">
-        <v>-2227</v>
+        <v>-2120</v>
       </c>
       <c r="C22" s="3">
-        <v>-2218</v>
+        <v>-2070</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" si="16"/>
-        <v>2186</v>
+        <f t="shared" si="6"/>
+        <v>2293</v>
       </c>
       <c r="E22" s="1">
-        <f t="shared" si="17"/>
-        <v>2195</v>
+        <f t="shared" si="7"/>
+        <v>2343</v>
       </c>
       <c r="F22" s="1">
         <f t="array" ref="F22">C22-B22</f>
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="G22" s="1">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="H22" s="1">
-        <f t="array" ref="H22">I22-G22</f>
-        <v>-4081</v>
+        <f t="shared" si="8"/>
+        <v>-4079</v>
       </c>
       <c r="I22" s="1">
-        <f t="array" ref="I22">H23</f>
-        <v>-4072</v>
+        <f t="array" ref="I22">H22+G22</f>
+        <v>-4029</v>
       </c>
       <c r="J22" s="1">
-        <f t="shared" si="18"/>
-        <v>332</v>
+        <f t="array" ref="J22">K21</f>
+        <v>335</v>
       </c>
       <c r="K22" s="1">
-        <f t="shared" si="19"/>
-        <v>341</v>
-      </c>
-      <c r="L22" s="1" t="s">
+        <f t="array" ref="K22">J22+G22</f>
+        <v>385</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="R22" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="V22" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="3">
-        <v>-2218</v>
-      </c>
-      <c r="C23" s="3">
-        <v>-2120</v>
+      <c r="B23" s="6">
+        <v>-2070</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-1600</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" si="16"/>
-        <v>2195</v>
+        <f>B23+4413</f>
+        <v>2343</v>
       </c>
       <c r="E23" s="1">
-        <f t="shared" si="17"/>
-        <v>2293</v>
+        <f>C23+4413</f>
+        <v>2813</v>
       </c>
       <c r="F23" s="1">
         <f t="array" ref="F23">C23-B23</f>
-        <v>98</v>
+        <v>470</v>
       </c>
       <c r="G23" s="1">
-        <v>98</v>
+        <v>470</v>
       </c>
       <c r="H23" s="1">
-        <f t="array" ref="H23">I23-G23</f>
-        <v>-4072</v>
+        <f t="shared" si="8"/>
+        <v>-4029</v>
       </c>
       <c r="I23" s="1">
-        <f t="array" ref="I23">H24</f>
-        <v>-3974</v>
+        <f t="array" ref="I23">H23+G23</f>
+        <v>-3559</v>
       </c>
       <c r="J23" s="1">
-        <f t="shared" si="18"/>
-        <v>341</v>
+        <f t="array" ref="J23">K22</f>
+        <v>385</v>
       </c>
       <c r="K23" s="1">
-        <f t="shared" si="19"/>
-        <v>439</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="V23" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="3">
-        <v>-2120</v>
-      </c>
-      <c r="C24" s="3">
-        <v>-2070</v>
+        <f t="array" ref="K23">J23+G23</f>
+        <v>855</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="6">
+        <v>-1600</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-1046</v>
       </c>
       <c r="D24" s="1">
-        <f t="shared" si="16"/>
-        <v>2293</v>
+        <f t="shared" ref="D24:D43" si="9">B24+4413</f>
+        <v>2813</v>
       </c>
       <c r="E24" s="1">
-        <f t="shared" si="17"/>
-        <v>2343</v>
+        <f t="shared" ref="E24:E42" si="10">C24+4413</f>
+        <v>3367</v>
       </c>
       <c r="F24" s="1">
         <f t="array" ref="F24">C24-B24</f>
-        <v>50</v>
+        <v>554</v>
       </c>
       <c r="G24" s="1">
-        <v>50</v>
+        <v>554</v>
       </c>
       <c r="H24" s="1">
-        <f t="array" ref="H24">I24-G24</f>
-        <v>-3974</v>
+        <f t="shared" si="8"/>
+        <v>-3559</v>
       </c>
       <c r="I24" s="1">
-        <f t="array" ref="I24">H25</f>
-        <v>-3924</v>
+        <f t="array" ref="I24">H24+G24</f>
+        <v>-3005</v>
       </c>
       <c r="J24" s="1">
-        <f t="shared" si="18"/>
-        <v>439</v>
+        <f t="array" ref="J24">K23</f>
+        <v>855</v>
       </c>
       <c r="K24" s="1">
-        <f t="shared" si="19"/>
-        <v>489</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="V24" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" ref="K24">J24+G24</f>
+        <v>1409</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B25" s="6">
-        <v>-2070</v>
+        <v>-1046</v>
       </c>
       <c r="C25" s="6">
-        <v>-1600</v>
+        <v>-771</v>
       </c>
       <c r="D25" s="1">
-        <f>B25+4413</f>
-        <v>2343</v>
+        <f t="shared" si="9"/>
+        <v>3367</v>
       </c>
       <c r="E25" s="1">
-        <f>C25+4413</f>
-        <v>2813</v>
+        <f t="shared" si="10"/>
+        <v>3642</v>
       </c>
       <c r="F25" s="1">
         <f t="array" ref="F25">C25-B25</f>
-        <v>470</v>
+        <v>275</v>
       </c>
       <c r="G25" s="1">
-        <v>470</v>
+        <v>275</v>
       </c>
       <c r="H25" s="1">
-        <f t="array" ref="H25">I25-G25</f>
-        <v>-3924</v>
+        <f t="shared" si="8"/>
+        <v>-3005</v>
       </c>
       <c r="I25" s="1">
-        <f t="array" ref="I25">H26</f>
-        <v>-3454</v>
+        <f t="array" ref="I25">H25+G25</f>
+        <v>-2730</v>
       </c>
       <c r="J25" s="1">
-        <f t="shared" ref="J25:J43" si="20">H25+4413</f>
-        <v>489</v>
+        <f t="array" ref="J25">K24</f>
+        <v>1409</v>
       </c>
       <c r="K25" s="1">
-        <f t="shared" ref="K25:K43" si="21">I25+4413</f>
-        <v>959</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" ref="K25">J25+G25</f>
+        <v>1684</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" s="6">
-        <v>-1600</v>
+        <v>-770</v>
       </c>
       <c r="C26" s="6">
-        <v>-1046</v>
+        <v>-221</v>
       </c>
       <c r="D26" s="1">
-        <f t="shared" ref="D26:D44" si="22">B26+4413</f>
-        <v>2813</v>
+        <f t="shared" si="9"/>
+        <v>3643</v>
       </c>
       <c r="E26" s="1">
-        <f t="shared" ref="E26:E44" si="23">C26+4413</f>
-        <v>3367</v>
+        <f t="shared" si="10"/>
+        <v>4192</v>
       </c>
       <c r="F26" s="1">
         <f t="array" ref="F26">C26-B26</f>
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="G26" s="1">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="H26" s="1">
-        <f t="array" ref="H26">I26-G26</f>
-        <v>-3454</v>
+        <f t="shared" si="8"/>
+        <v>-2730</v>
       </c>
       <c r="I26" s="1">
-        <f t="array" ref="I26">H27</f>
-        <v>-2900</v>
+        <f t="array" ref="I26">H26+G26</f>
+        <v>-2181</v>
       </c>
       <c r="J26" s="1">
-        <f t="shared" si="20"/>
-        <v>959</v>
+        <f t="array" ref="J26">K25</f>
+        <v>1684</v>
       </c>
       <c r="K26" s="1">
-        <f t="shared" si="21"/>
-        <v>1513</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="U26" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="V26" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" ref="K26">J26+G26</f>
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27" s="6">
-        <v>-1046</v>
+        <v>-221</v>
       </c>
       <c r="C27" s="6">
-        <v>-771</v>
+        <v>-207</v>
       </c>
       <c r="D27" s="1">
-        <f t="shared" si="22"/>
-        <v>3367</v>
+        <f t="shared" si="9"/>
+        <v>4192</v>
       </c>
       <c r="E27" s="1">
-        <f t="shared" si="23"/>
-        <v>3642</v>
+        <f t="shared" si="10"/>
+        <v>4206</v>
       </c>
       <c r="F27" s="1">
         <f t="array" ref="F27">C27-B27</f>
-        <v>275</v>
+        <v>14</v>
       </c>
       <c r="G27" s="1">
-        <v>275</v>
+        <v>14</v>
       </c>
       <c r="H27" s="1">
-        <f t="array" ref="H27">I27-G27</f>
-        <v>-2900</v>
+        <f t="shared" si="8"/>
+        <v>-2181</v>
       </c>
       <c r="I27" s="1">
-        <f t="array" ref="I27">H28</f>
-        <v>-2625</v>
+        <f t="array" ref="I27">H27+G27</f>
+        <v>-2167</v>
       </c>
       <c r="J27" s="1">
-        <f t="shared" si="20"/>
-        <v>1513</v>
+        <f t="array" ref="J27">K26</f>
+        <v>2233</v>
       </c>
       <c r="K27" s="1">
-        <f t="shared" si="21"/>
-        <v>1788</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="V27" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" ref="K27">J27+G27</f>
+        <v>2247</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B28" s="6">
-        <v>-770</v>
+        <v>-202</v>
       </c>
       <c r="C28" s="6">
-        <v>-221</v>
+        <v>8</v>
       </c>
       <c r="D28" s="1">
-        <f t="shared" si="22"/>
-        <v>3643</v>
+        <f t="shared" si="9"/>
+        <v>4211</v>
       </c>
       <c r="E28" s="1">
-        <f t="shared" si="23"/>
-        <v>4192</v>
+        <f t="shared" si="10"/>
+        <v>4421</v>
       </c>
       <c r="F28" s="1">
         <f t="array" ref="F28">C28-B28</f>
-        <v>549</v>
+        <v>210</v>
       </c>
       <c r="G28" s="1">
-        <v>549</v>
+        <v>1289</v>
       </c>
       <c r="H28" s="1">
-        <f t="array" ref="H28">I28-G28</f>
-        <v>-2625</v>
+        <f t="shared" si="8"/>
+        <v>-2167</v>
       </c>
       <c r="I28" s="1">
-        <f t="array" ref="I28">H29</f>
-        <v>-2076</v>
+        <f t="array" ref="I28">H28+G28</f>
+        <v>-878</v>
       </c>
       <c r="J28" s="1">
-        <f t="shared" si="20"/>
-        <v>1788</v>
+        <f t="array" ref="J28">K27</f>
+        <v>2247</v>
       </c>
       <c r="K28" s="1">
-        <f t="shared" si="21"/>
-        <v>2337</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="S28" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="T28" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="U28" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="V28" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" ref="K28">J28+G28</f>
+        <v>3536</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B29" s="6">
-        <v>-221</v>
+        <v>9</v>
       </c>
       <c r="C29" s="6">
-        <v>-207</v>
+        <v>23</v>
       </c>
       <c r="D29" s="1">
-        <f t="shared" si="22"/>
-        <v>4192</v>
+        <f t="shared" si="9"/>
+        <v>4422</v>
       </c>
       <c r="E29" s="1">
-        <f t="shared" si="23"/>
-        <v>4206</v>
+        <f t="shared" si="10"/>
+        <v>4436</v>
       </c>
       <c r="F29" s="1">
         <f t="array" ref="F29">C29-B29</f>
@@ -4063,902 +3622,605 @@
         <v>14</v>
       </c>
       <c r="H29" s="1">
-        <f t="array" ref="H29">I29-G29</f>
-        <v>-2076</v>
+        <f t="shared" si="8"/>
+        <v>-878</v>
       </c>
       <c r="I29" s="1">
-        <f t="array" ref="I29">H30</f>
-        <v>-2062</v>
+        <f t="array" ref="I29">H29+G29</f>
+        <v>-864</v>
       </c>
       <c r="J29" s="1">
-        <f t="shared" si="20"/>
-        <v>2337</v>
+        <f t="array" ref="J29">K28</f>
+        <v>3536</v>
       </c>
       <c r="K29" s="1">
-        <f t="shared" si="21"/>
-        <v>2351</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="U29" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="V29" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" ref="K29">J29+G29</f>
+        <v>3550</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" s="6">
-        <v>-202</v>
+        <v>25</v>
       </c>
       <c r="C30" s="6">
-        <v>8</v>
+        <v>220</v>
       </c>
       <c r="D30" s="1">
-        <f t="shared" si="22"/>
-        <v>4211</v>
+        <f t="shared" si="9"/>
+        <v>4438</v>
       </c>
       <c r="E30" s="1">
-        <f t="shared" si="23"/>
-        <v>4421</v>
+        <f t="shared" si="10"/>
+        <v>4633</v>
       </c>
       <c r="F30" s="1">
         <f t="array" ref="F30">C30-B30</f>
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="G30" s="1">
-        <v>1184</v>
+        <v>597</v>
       </c>
       <c r="H30" s="1">
-        <f t="array" ref="H30">I30-G30</f>
-        <v>-2062</v>
+        <f t="shared" si="8"/>
+        <v>-864</v>
       </c>
       <c r="I30" s="1">
-        <f t="array" ref="I30">H31</f>
-        <v>-878</v>
+        <f t="array" ref="I30">H30+G30</f>
+        <v>-267</v>
       </c>
       <c r="J30" s="1">
-        <f t="shared" si="20"/>
-        <v>2351</v>
+        <f t="array" ref="J30">K29</f>
+        <v>3550</v>
       </c>
       <c r="K30" s="1">
-        <f t="shared" si="21"/>
-        <v>3535</v>
+        <f t="array" ref="K30">J30+G30</f>
+        <v>4147</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="R30" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="V30" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31" s="6">
-        <v>9</v>
+        <v>220</v>
       </c>
       <c r="C31" s="6">
-        <v>23</v>
+        <v>280</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" si="22"/>
-        <v>4422</v>
+        <f t="shared" si="9"/>
+        <v>4633</v>
       </c>
       <c r="E31" s="1">
-        <f t="shared" si="23"/>
-        <v>4436</v>
+        <f t="shared" si="10"/>
+        <v>4693</v>
       </c>
       <c r="F31" s="1">
         <f t="array" ref="F31">C31-B31</f>
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="G31" s="1">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="H31" s="1">
-        <f t="array" ref="H31">I31-G31</f>
-        <v>-878</v>
+        <f t="shared" si="8"/>
+        <v>-267</v>
       </c>
       <c r="I31" s="1">
-        <f t="array" ref="I31">H32</f>
-        <v>-864</v>
+        <f t="array" ref="I31">H31+G31</f>
+        <v>-207</v>
       </c>
       <c r="J31" s="1">
-        <f t="shared" si="20"/>
-        <v>3535</v>
+        <f t="array" ref="J31">K30</f>
+        <v>4147</v>
       </c>
       <c r="K31" s="1">
-        <f t="shared" si="21"/>
-        <v>3549</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="U31" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="V31" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" ref="K31">J31+G31</f>
+        <v>4207</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B32" s="6">
-        <v>25</v>
+        <v>265</v>
       </c>
       <c r="C32" s="6">
-        <v>220</v>
+        <v>316</v>
       </c>
       <c r="D32" s="1">
-        <f t="shared" si="22"/>
-        <v>4438</v>
+        <f t="shared" si="9"/>
+        <v>4678</v>
       </c>
       <c r="E32" s="1">
-        <f t="shared" si="23"/>
-        <v>4633</v>
+        <f t="shared" si="10"/>
+        <v>4729</v>
       </c>
       <c r="F32" s="1">
         <f t="array" ref="F32">C32-B32</f>
-        <v>195</v>
+        <v>51</v>
       </c>
       <c r="G32" s="1">
-        <v>597</v>
+        <v>51</v>
       </c>
       <c r="H32" s="1">
-        <f t="array" ref="H32">I32-G32</f>
-        <v>-864</v>
+        <f t="shared" si="8"/>
+        <v>-207</v>
       </c>
       <c r="I32" s="1">
-        <f t="array" ref="I32">H33</f>
-        <v>-267</v>
+        <f t="array" ref="I32">H32+G32</f>
+        <v>-156</v>
       </c>
       <c r="J32" s="1">
-        <f t="shared" si="20"/>
-        <v>3549</v>
+        <f t="array" ref="J32">K31</f>
+        <v>4207</v>
       </c>
       <c r="K32" s="1">
-        <f t="shared" si="21"/>
-        <v>4146</v>
-      </c>
-      <c r="L32" s="1" t="s">
+        <f t="array" ref="K32">J32+G32</f>
+        <v>4258</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R32" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="V32" s="1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="B33" s="6">
-        <v>220</v>
+        <v>317</v>
       </c>
       <c r="C33" s="6">
-        <v>280</v>
+        <v>420</v>
       </c>
       <c r="D33" s="1">
-        <f t="shared" si="22"/>
-        <v>4633</v>
+        <f t="shared" si="9"/>
+        <v>4730</v>
       </c>
       <c r="E33" s="1">
-        <f t="shared" si="23"/>
-        <v>4693</v>
+        <f t="shared" si="10"/>
+        <v>4833</v>
       </c>
       <c r="F33" s="1">
         <f t="array" ref="F33">C33-B33</f>
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="G33" s="1">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="H33" s="1">
-        <f t="array" ref="H33">I33-G33</f>
-        <v>-267</v>
+        <f t="shared" si="8"/>
+        <v>-156</v>
       </c>
       <c r="I33" s="1">
-        <f t="array" ref="I33">H34</f>
-        <v>-207</v>
+        <f t="array" ref="I33">H33+G33</f>
+        <v>-53</v>
       </c>
       <c r="J33" s="1">
-        <f t="shared" si="20"/>
-        <v>4146</v>
+        <f t="array" ref="J33">K32</f>
+        <v>4258</v>
       </c>
       <c r="K33" s="1">
-        <f t="shared" si="21"/>
-        <v>4206</v>
-      </c>
-      <c r="R33" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="V33" s="1" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" ref="K33">J33+G33</f>
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="6">
-        <v>265</v>
+        <v>420</v>
       </c>
       <c r="C34" s="6">
-        <v>316</v>
+        <v>589</v>
       </c>
       <c r="D34" s="1">
-        <f t="shared" si="22"/>
-        <v>4678</v>
+        <f t="shared" si="9"/>
+        <v>4833</v>
       </c>
       <c r="E34" s="1">
-        <f t="shared" si="23"/>
-        <v>4729</v>
+        <f t="shared" si="10"/>
+        <v>5002</v>
       </c>
       <c r="F34" s="1">
         <f t="array" ref="F34">C34-B34</f>
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="G34" s="1">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="H34" s="1">
-        <f t="array" ref="H34">I34-G34</f>
-        <v>-207</v>
+        <f t="shared" si="8"/>
+        <v>-53</v>
       </c>
       <c r="I34" s="1">
-        <f t="array" ref="I34">H35</f>
-        <v>-156</v>
+        <f t="array" ref="I34">H34+G34</f>
+        <v>116</v>
       </c>
       <c r="J34" s="1">
-        <f t="shared" si="20"/>
-        <v>4206</v>
+        <f t="array" ref="J34">K33</f>
+        <v>4361</v>
       </c>
       <c r="K34" s="1">
-        <f t="shared" si="21"/>
-        <v>4257</v>
-      </c>
-      <c r="R34" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="V34" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" ref="K34">J34+G34</f>
+        <v>4530</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="6">
-        <v>317</v>
+        <v>581</v>
       </c>
       <c r="C35" s="6">
-        <v>420</v>
+        <v>618</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" si="22"/>
-        <v>4730</v>
+        <f t="shared" si="9"/>
+        <v>4994</v>
       </c>
       <c r="E35" s="1">
-        <f t="shared" si="23"/>
-        <v>4833</v>
+        <f t="shared" si="10"/>
+        <v>5031</v>
       </c>
       <c r="F35" s="1">
         <f t="array" ref="F35">C35-B35</f>
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="G35" s="1">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="H35" s="1">
-        <f t="array" ref="H35">I35-G35</f>
-        <v>-156</v>
+        <f t="shared" si="8"/>
+        <v>116</v>
       </c>
       <c r="I35" s="1">
-        <f t="array" ref="I35">H36</f>
-        <v>-53</v>
+        <f t="array" ref="I35">H35+G35</f>
+        <v>116</v>
       </c>
       <c r="J35" s="1">
-        <f t="shared" si="20"/>
-        <v>4257</v>
+        <f t="array" ref="J35">K34</f>
+        <v>4530</v>
       </c>
       <c r="K35" s="1">
-        <f t="shared" si="21"/>
-        <v>4360</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="S35" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="T35" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="U35" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="V35" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" ref="K35">J35+G35</f>
+        <v>4530</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="6">
-        <v>420</v>
+        <v>618</v>
       </c>
       <c r="C36" s="6">
-        <v>589</v>
+        <v>907</v>
       </c>
       <c r="D36" s="1">
-        <f t="shared" si="22"/>
-        <v>4833</v>
+        <f t="shared" si="9"/>
+        <v>5031</v>
       </c>
       <c r="E36" s="1">
-        <f t="shared" si="23"/>
-        <v>5002</v>
+        <f t="shared" si="10"/>
+        <v>5320</v>
       </c>
       <c r="F36" s="1">
         <f t="array" ref="F36">C36-B36</f>
-        <v>169</v>
+        <v>289</v>
       </c>
       <c r="G36" s="1">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="H36" s="1">
-        <f t="array" ref="H36">I36-G36</f>
-        <v>-53</v>
+        <f t="shared" si="8"/>
+        <v>116</v>
       </c>
       <c r="I36" s="1">
-        <f t="array" ref="I36">H37</f>
+        <f t="array" ref="I36">H36+G36</f>
         <v>116</v>
       </c>
       <c r="J36" s="1">
-        <f t="shared" si="20"/>
-        <v>4360</v>
+        <f t="array" ref="J36">K35</f>
+        <v>4530</v>
       </c>
       <c r="K36" s="1">
-        <f t="shared" si="21"/>
-        <v>4529</v>
-      </c>
-      <c r="R36" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="S36" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="T36" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="U36" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="V36" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="37" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" ref="K36">J36+G36</f>
+        <v>4530</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="6">
-        <v>581</v>
+        <v>907</v>
       </c>
       <c r="C37" s="6">
-        <v>618</v>
+        <v>960</v>
       </c>
       <c r="D37" s="1">
-        <f t="shared" si="22"/>
-        <v>4994</v>
+        <f t="shared" si="9"/>
+        <v>5320</v>
       </c>
       <c r="E37" s="1">
-        <f t="shared" si="23"/>
-        <v>5031</v>
+        <f t="shared" si="10"/>
+        <v>5373</v>
       </c>
       <c r="F37" s="1">
         <f t="array" ref="F37">C37-B37</f>
+        <v>53</v>
+      </c>
+      <c r="G37" s="1">
+        <v>53</v>
+      </c>
+      <c r="H37" s="1">
+        <f t="shared" si="8"/>
+        <v>116</v>
+      </c>
+      <c r="I37" s="1">
+        <f t="array" ref="I37">H37+G37</f>
+        <v>169</v>
+      </c>
+      <c r="J37" s="1">
+        <f t="array" ref="J37">K36</f>
+        <v>4530</v>
+      </c>
+      <c r="K37" s="1">
+        <f t="array" ref="K37">J37+G37</f>
+        <v>4583</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G37" s="1">
-        <v>0</v>
-      </c>
-      <c r="H37" s="1">
-        <f t="array" ref="H37">I37-G37</f>
-        <v>116</v>
-      </c>
-      <c r="I37" s="1">
-        <f t="array" ref="I37">H38</f>
-        <v>116</v>
-      </c>
-      <c r="J37" s="1">
-        <f t="shared" si="20"/>
-        <v>4529</v>
-      </c>
-      <c r="K37" s="1">
-        <f t="shared" si="21"/>
-        <v>4529</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R37" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="S37" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="B38" s="6">
-        <v>618</v>
+        <v>960</v>
       </c>
       <c r="C38" s="6">
-        <v>907</v>
+        <v>1127</v>
       </c>
       <c r="D38" s="1">
-        <f t="shared" si="22"/>
-        <v>5031</v>
+        <f t="shared" si="9"/>
+        <v>5373</v>
       </c>
       <c r="E38" s="1">
-        <f t="shared" si="23"/>
-        <v>5320</v>
+        <f t="shared" si="10"/>
+        <v>5540</v>
       </c>
       <c r="F38" s="1">
         <f t="array" ref="F38">C38-B38</f>
-        <v>289</v>
+        <v>167</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H38" s="1">
-        <f t="array" ref="H38">I38-G38</f>
-        <v>116</v>
+        <f t="shared" si="8"/>
+        <v>169</v>
       </c>
       <c r="I38" s="1">
-        <f t="array" ref="I38">H39</f>
-        <v>116</v>
+        <f t="array" ref="I38">H38+G38</f>
+        <v>1269</v>
       </c>
       <c r="J38" s="1">
-        <f t="shared" si="20"/>
-        <v>4529</v>
+        <f t="array" ref="J38">K37</f>
+        <v>4583</v>
       </c>
       <c r="K38" s="1">
-        <f t="shared" si="21"/>
-        <v>4529</v>
+        <f t="array" ref="K38">J38+G38</f>
+        <v>5683</v>
       </c>
       <c r="L38" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="R38" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="S38" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="V38" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="B39" s="6">
-        <v>907</v>
+        <v>1127</v>
       </c>
       <c r="C39" s="6">
-        <v>960</v>
+        <v>1279</v>
       </c>
       <c r="D39" s="1">
-        <f t="shared" si="22"/>
-        <v>5320</v>
+        <f t="shared" si="9"/>
+        <v>5540</v>
       </c>
       <c r="E39" s="1">
-        <f t="shared" si="23"/>
-        <v>5373</v>
+        <f t="shared" si="10"/>
+        <v>5692</v>
       </c>
       <c r="F39" s="1">
         <f t="array" ref="F39">C39-B39</f>
-        <v>53</v>
+        <v>152</v>
       </c>
       <c r="G39" s="1">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H39" s="1">
-        <f t="array" ref="H39">I39-G39</f>
-        <v>116</v>
+        <f t="shared" si="8"/>
+        <v>1269</v>
       </c>
       <c r="I39" s="1">
-        <f t="array" ref="I39">H40</f>
-        <v>169</v>
+        <f t="array" ref="I39">H39+G39</f>
+        <v>1269</v>
       </c>
       <c r="J39" s="1">
-        <f t="shared" si="20"/>
-        <v>4529</v>
+        <f t="array" ref="J39">K38</f>
+        <v>5683</v>
       </c>
       <c r="K39" s="1">
-        <f t="shared" si="21"/>
-        <v>4582</v>
-      </c>
-      <c r="R39" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="S39" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="U39" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="V39" s="1" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" ref="K39">J39+G39</f>
+        <v>5683</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" s="6">
-        <v>960</v>
+        <v>1271</v>
       </c>
       <c r="C40" s="6">
-        <v>1127</v>
+        <v>1368</v>
       </c>
       <c r="D40" s="1">
-        <f t="shared" si="22"/>
-        <v>5373</v>
+        <f t="shared" si="9"/>
+        <v>5684</v>
       </c>
       <c r="E40" s="1">
-        <f t="shared" si="23"/>
-        <v>5540</v>
+        <f t="shared" si="10"/>
+        <v>5781</v>
       </c>
       <c r="F40" s="1">
         <f t="array" ref="F40">C40-B40</f>
-        <v>167</v>
+        <v>97</v>
       </c>
       <c r="G40" s="1">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1">
-        <f t="array" ref="H40">I40-G40</f>
-        <v>169</v>
+        <f t="shared" si="8"/>
+        <v>1269</v>
       </c>
       <c r="I40" s="1">
-        <f t="array" ref="I40">H41</f>
+        <f t="array" ref="I40">H40+G40</f>
         <v>1269</v>
       </c>
       <c r="J40" s="1">
-        <f t="shared" si="20"/>
-        <v>4582</v>
+        <f t="array" ref="J40">K39</f>
+        <v>5683</v>
       </c>
       <c r="K40" s="1">
-        <f t="shared" si="21"/>
-        <v>5682</v>
+        <f t="array" ref="K40">J40+G40</f>
+        <v>5683</v>
       </c>
       <c r="L40" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="R40" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="T40" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="U40" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="V40" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
       <c r="B41" s="6">
-        <v>1127</v>
+        <v>1368</v>
       </c>
       <c r="C41" s="6">
-        <v>1279</v>
+        <v>1644</v>
       </c>
       <c r="D41" s="1">
-        <f t="shared" si="22"/>
-        <v>5540</v>
+        <f t="shared" si="9"/>
+        <v>5781</v>
       </c>
       <c r="E41" s="1">
-        <f t="shared" si="23"/>
-        <v>5692</v>
+        <f t="shared" si="10"/>
+        <v>6057</v>
       </c>
       <c r="F41" s="1">
         <f t="array" ref="F41">C41-B41</f>
-        <v>152</v>
+        <v>276</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="H41" s="1">
-        <f t="array" ref="H41">I41-G41</f>
+        <f t="shared" si="8"/>
         <v>1269</v>
       </c>
       <c r="I41" s="1">
-        <f t="array" ref="I41">H42</f>
-        <v>1269</v>
+        <f t="array" ref="I41">H41+G41</f>
+        <v>1847</v>
       </c>
       <c r="J41" s="1">
-        <f t="shared" si="20"/>
-        <v>5682</v>
+        <f t="array" ref="J41">K40</f>
+        <v>5683</v>
       </c>
       <c r="K41" s="1">
-        <f t="shared" si="21"/>
-        <v>5682</v>
-      </c>
-      <c r="R41" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="S41" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="T41" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="U41" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="V41" s="1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="array" ref="K41">J41+G41</f>
+        <v>6261</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B42" s="6">
-        <v>1271</v>
+        <v>1644</v>
       </c>
       <c r="C42" s="6">
-        <v>1368</v>
+        <v>1912</v>
       </c>
       <c r="D42" s="1">
-        <f t="shared" si="22"/>
-        <v>5684</v>
+        <f t="shared" si="9"/>
+        <v>6057</v>
       </c>
       <c r="E42" s="1">
-        <f t="shared" si="23"/>
-        <v>5781</v>
+        <f t="shared" si="10"/>
+        <v>6325</v>
       </c>
       <c r="F42" s="1">
         <f t="array" ref="F42">C42-B42</f>
-        <v>97</v>
+        <v>268</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H42" s="1">
-        <f t="array" ref="H42">I42-G42</f>
-        <v>1269</v>
+        <f t="shared" si="8"/>
+        <v>1847</v>
       </c>
       <c r="I42" s="1">
-        <f t="array" ref="I42">H43</f>
-        <v>1269</v>
+        <f t="array" ref="I42">H42+G42</f>
+        <v>1912</v>
       </c>
       <c r="J42" s="1">
-        <f t="shared" si="20"/>
-        <v>5682</v>
+        <f t="array" ref="J42">K41</f>
+        <v>6261</v>
       </c>
       <c r="K42" s="1">
-        <f t="shared" si="21"/>
-        <v>5682</v>
+        <f t="array" ref="K42">J42+G42</f>
+        <v>6326</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="R42" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="S42" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="T42" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="U42" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="43" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B43" s="6">
-        <v>1368</v>
-      </c>
-      <c r="C43" s="6">
-        <v>1644</v>
+    </row>
+    <row r="43" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="B43" s="1">
+        <v>2026</v>
       </c>
       <c r="D43" s="1">
-        <f t="shared" si="22"/>
-        <v>5781</v>
-      </c>
-      <c r="E43" s="1">
-        <f t="shared" si="23"/>
-        <v>6057</v>
-      </c>
-      <c r="F43" s="1">
-        <f t="array" ref="F43">C43-B43</f>
-        <v>276</v>
-      </c>
-      <c r="G43" s="1">
-        <v>578</v>
-      </c>
-      <c r="H43" s="1">
-        <f t="array" ref="H43">I43-G43</f>
-        <v>1269</v>
-      </c>
-      <c r="I43" s="1">
-        <f t="array" ref="I43">H44</f>
-        <v>1847</v>
-      </c>
-      <c r="J43" s="1">
-        <f t="shared" si="20"/>
-        <v>5682</v>
-      </c>
-      <c r="K43" s="1">
-        <f t="shared" si="21"/>
-        <v>6260</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="S43" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="T43" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="V43" s="1" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B44" s="6">
-        <v>1644</v>
-      </c>
-      <c r="C44" s="6">
-        <v>1912</v>
-      </c>
-      <c r="D44" s="1">
-        <f t="shared" si="22"/>
-        <v>6057</v>
-      </c>
-      <c r="E44" s="1">
-        <f t="shared" si="23"/>
-        <v>6325</v>
-      </c>
-      <c r="F44" s="1">
-        <f t="array" ref="F44">C44-B44</f>
-        <v>268</v>
-      </c>
-      <c r="G44" s="1">
-        <v>65</v>
-      </c>
-      <c r="H44" s="1">
-        <f t="array" ref="H44">I44-G44</f>
-        <v>1847</v>
-      </c>
-      <c r="I44" s="1">
-        <v>1912</v>
-      </c>
-      <c r="J44" s="1">
-        <f>H44+4413</f>
-        <v>6260</v>
-      </c>
-      <c r="K44" s="1">
-        <f>I44+4413</f>
-        <v>6325</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>49</v>
+        <f t="shared" si="9"/>
+        <v>6439</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:V1"/>
-  </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4968,23 +4230,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7293523-8A88-4FA8-8AD8-9CEC8BA3DC9C}">
   <dimension ref="A1:B74"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.26953125" customWidth="1"/>
-    <col min="2" max="2" width="84.54296875" customWidth="1"/>
+    <col min="1" max="1" width="6.21875" customWidth="1"/>
+    <col min="2" max="2" width="84.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4992,7 +4254,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -5000,7 +4262,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -5008,7 +4270,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>398</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -5016,7 +4278,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -5024,7 +4286,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -5032,7 +4294,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -5040,7 +4302,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -5048,7 +4310,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -5056,7 +4318,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -5064,7 +4326,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -5072,7 +4334,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -5080,7 +4342,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -5088,7 +4350,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>407</v>
+        <v>385</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -5096,7 +4358,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -5104,7 +4366,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -5112,7 +4374,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -5120,7 +4382,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -5128,7 +4390,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -5136,7 +4398,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -5144,7 +4406,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -5152,7 +4414,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -5160,7 +4422,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -5168,7 +4430,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -5176,7 +4438,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -5184,7 +4446,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -5192,7 +4454,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>374</v>
+        <v>352</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -5200,7 +4462,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>375</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -5208,7 +4470,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -5216,7 +4478,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -5224,7 +4486,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -5232,7 +4494,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -5240,7 +4502,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>384</v>
+        <v>362</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -5248,7 +4510,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>383</v>
+        <v>361</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -5256,7 +4518,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -5264,7 +4526,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>388</v>
+        <v>366</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -5272,7 +4534,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>389</v>
+        <v>367</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -5280,7 +4542,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>390</v>
+        <v>368</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -5288,7 +4550,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>391</v>
+        <v>369</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -5296,7 +4558,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>392</v>
+        <v>370</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -5304,7 +4566,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>393</v>
+        <v>371</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -5312,7 +4574,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>396</v>
+        <v>374</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -5320,7 +4582,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>394</v>
+        <v>372</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -5328,7 +4590,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>395</v>
+        <v>373</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -5336,7 +4598,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>397</v>
+        <v>375</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -5344,7 +4606,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>402</v>
+        <v>380</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -5352,7 +4614,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>400</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -5360,7 +4622,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>401</v>
+        <v>379</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -5368,7 +4630,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>403</v>
+        <v>381</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -5376,7 +4638,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>404</v>
+        <v>382</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -5384,7 +4646,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>405</v>
+        <v>383</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -5392,7 +4654,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>406</v>
+        <v>384</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -5400,7 +4662,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>408</v>
+        <v>386</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -5408,7 +4670,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>409</v>
+        <v>387</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -5416,7 +4678,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>410</v>
+        <v>388</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -5424,7 +4686,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>411</v>
+        <v>389</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -5432,7 +4694,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>412</v>
+        <v>390</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -5440,7 +4702,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>413</v>
+        <v>391</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -5448,7 +4710,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>414</v>
+        <v>392</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -5456,7 +4718,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>415</v>
+        <v>393</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -5464,7 +4726,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>416</v>
+        <v>394</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -5472,7 +4734,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>417</v>
+        <v>395</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -5480,7 +4742,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>418</v>
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -5488,7 +4750,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>419</v>
+        <v>397</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -5496,7 +4758,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>420</v>
+        <v>398</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -5504,7 +4766,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>421</v>
+        <v>399</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -5512,7 +4774,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>422</v>
+        <v>400</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -5520,7 +4782,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>423</v>
+        <v>401</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -5528,7 +4790,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>424</v>
+        <v>402</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -5536,7 +4798,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>425</v>
+        <v>403</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -5544,7 +4806,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -5552,7 +4814,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>427</v>
+        <v>405</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -5560,7 +4822,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>428</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -5573,27 +4835,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA240CE6-07FC-4E34-B886-D2C08CA4BB15}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.7265625" customWidth="1"/>
-    <col min="2" max="2" width="52.90625" customWidth="1"/>
-    <col min="3" max="3" width="57.7265625" customWidth="1"/>
+    <col min="1" max="1" width="5.77734375" customWidth="1"/>
+    <col min="2" max="2" width="52.88671875" customWidth="1"/>
+    <col min="3" max="3" width="57.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5601,10 +4863,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -5612,10 +4874,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -5623,10 +4885,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -5634,10 +4896,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -5645,10 +4907,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -5665,860 +4927,860 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E2970B-D0B7-4172-9BDF-6B6D3315D629}">
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.81640625" customWidth="1"/>
+    <col min="1" max="1" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="E1" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="F1" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="F2" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="F3" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="F4" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="C5" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="D5" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="F5" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="F6" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C7" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="E7" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="F7" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="B8" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="E8" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="F8" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="B9" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="C9" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="D9" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="E9" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="F9" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="B10" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="C10" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="E10" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="F10" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="C11" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="D11" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E11" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="F11" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="C12" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="D12" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="E12" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="F12" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="C13" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="D13" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="E13" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="F13" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="D14" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="E14" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="F14" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="D15" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="E15" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F15" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="C16" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="D16" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="E16" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="F16" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="C17" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="D17" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="E17" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="F17" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="C18" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="D18" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="E18" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="F18" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="C19" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="D19" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="E19" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F19" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="C20" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="D20" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="E20" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="F20" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="C21" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="D21" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="E21" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="F21" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="C22" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="D22" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="E22" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="F22" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="C23" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="D23" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="E23" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="F23" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="C24" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="D24" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="E24" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="F24" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="D25" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="E25" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="F25" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="B26" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="C26" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="D26" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="E26" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="F26" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C27" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="D27" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="E27" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="F27" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="C28" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="D28" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="E28" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="F28" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="C29" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="D29" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="E29" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="F29" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="C30" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="E30" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="F30" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="B31" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="C31" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="D31" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="E31" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="F31" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="B32" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="C32" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="D32" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="E32" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="F32" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="C33" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="D33" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="E33" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="F33" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="C34" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="D34" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="E34" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="F34" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="C35" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="D35" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="E35" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="F35" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="C36" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="D36" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="E36" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="F36" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="C37" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="D37" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="C38" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="D38" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="E38" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="F38" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="C39" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="D39" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="E39" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="F39" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="C40" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="D40" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="E40" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="F40" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="C41" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="D41" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="E41" t="s">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="F41" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="C42" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="D42" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="E42" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="B43" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="C43" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="D43" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="E43" t="s">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="F43" t="s">
-        <v>367</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
